--- a/assessments/FinOps++/assessment.xlsx
+++ b/assessments/FinOps++/assessment.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="423">
   <si>
     <t>Sum of Weights</t>
   </si>
@@ -962,6 +962,9 @@
   </si>
   <si>
     <t>1.6.1</t>
+  </si>
+  <si>
+    <t>1.9.0</t>
   </si>
   <si>
     <t>* Select which teams or groups are in scope for the planned assessments
@@ -1202,6 +1205,32 @@
 </t>
   </si>
   <si>
+    <t>Denominator: all anomalies detected during the review period. A field item is met when the field is
+populated on 90% or more of those records.
+* Single system of record
+* Scope fields populated (billing account, service, region, and a named accountable owner)
+* Impact fields populated (variance amount in the reporting currency, and the start and end of the
+  period the variance covers)
+* Timeline fields populated (first occurrence, detection, notification, and resolution timestamps)
+* Disposition field populated (true, expected change, or false)
+* Retention and queryability (records retained for at least 13 months and queryable by scope,
+  disposition, and root cause)
+10*Ceil(x/6)</t>
+  </si>
+  <si>
+    <t>Denominator: anomalies recorded with a true positive disposition during the review period. Items 1
+through 4 are met when the stated field is populated on 90% or more of those records.
+1. Owner and due date (each record carries a named accountable owner and an analysis due date)
+2. Root cause recorded (each record carries a root cause entry naming the change that triggered it)
+3. Cause classified (each root cause assigned exactly one category from a published, fixed
+   category list)
+4. Remediation recorded (each record carries a remediation action, its completion date, and the
+   measured spend delta over the period following the fix)
+5. Preventive control registered (every cause category observed 3 or more times in the trailing
+   12 months has a linked policy, guardrail, budget, or detection rule)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
     <t>* Number of detections per time period
 * Number of detections over threshold
 * Time to send notifications to stakeholders
@@ -1213,6 +1242,25 @@
 10*Ceil(x/8)</t>
   </si>
   <si>
+    <t>* Weighted sum
+  Alert precision (score x4),
+  Missed anomalies (score x3),
+  Tuning cadence (score x2),
+  Tuning governance (score x1).
+  Max raw (50)
+* Alert_Precision: Alerts confirmed as true positives divided by all alerts raised in the review period
+  (0=Not measured, 1&lt;50%, 2=50-69%, 3=70-84%, 4=85-94%, 5=95%+)
+* Missed_Anomalies: Share of anomalies first found by invoice review, budget variance, or an owner
+  (0=Not measured, 1&gt;25%, 2=10-25%, 3=5-9%, 4=1-4%, 5&lt;1%)
+* Tuning_Cadence: How often thresholds are reviewed and adjusted against observed outcomes
+  (0=Never, 1=Ad-hoc, 2=Annual, 3=Quarterly, 4=Monthly, 5=Continuous or automated)
+* Tuning_Governance: How a threshold change is decided and recorded
+  (0=Undocumented, 1=Changed by one person, 2=Documented with rationale,
+  3=Reviewed with the alert recipients, 4=Version controlled and auditable,
+  5=Version controlled and replayed against historical anomalies before release)
+* Output Range (0-50)</t>
+  </si>
+  <si>
     <t xml:space="preserve">* Define data quality (complete, valid, etc.)
 * Manual quality checks
 * Automated checks (null % on required fields/tags)
@@ -1249,10 +1297,10 @@
 10*Ceil(x/4)</t>
   </si>
   <si>
-    <t>* Data based on existing patterns
-* Proactive investigations and interviews with teams
-* Proactive self reporting by the business and/or teams
-* 100% catch rate of spikes before they happen
+    <t>* Collect data based on existing patterns observed in spend
+* Conduct proactive investigations and interviews with teams
+* Gather existing self reporting by the business and/or teams
+* Factor in expected increases to the forecast model
 10*Ceil(x/4)</t>
   </si>
   <si>
@@ -1420,6 +1468,9 @@
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': '1 item completed'}, {'Score': 3, 'Condition': '2 items completed'}, {'Score': 4, 'Condition': '3 items completed'}, {'Score': 5, 'Condition': '4 items completed'}, {'Score': 7, 'Condition': '5 items completed'}, {'Score': 8, 'Condition': '6 items completed'}, {'Score': 9, 'Condition': '7 items completed'}, {'Score': 10, 'Condition': '8 items completed'}]</t>
   </si>
   <si>
+    <t>[{'Score': 0, 'Condition': 'Low Maturity, Score Range (0-14)'}, {'Score': 4, 'Condition': 'Developing, Score Range (15-30)'}, {'Score': 7, 'Condition': 'Established, Score Range (31-42)'}, {'Score': 10, 'Condition': 'Optimizing, Score Range (43-50)'}]</t>
+  </si>
+  <si>
     <t>[{'Score': 0, 'Condition': 'Never'}, {'Score': 1, 'Condition': 'Monthly or greater'}, {'Score': 2, 'Condition': 'More than a week'}, {'Score': 3, 'Condition': '7 days'}, {'Score': 4, 'Condition': '5 days'}, {'Score': 6, 'Condition': '2 days'}, {'Score': 8, 'Condition': '1 day'}, {'Score': 10, 'Condition': 'Instant'}]</t>
   </si>
   <si>
@@ -1481,6 +1532,9 @@
   </si>
   <si>
     <t>0: No alerting to any owners</t>
+  </si>
+  <si>
+    <t>0: Low Maturity. Score Range (0-14)</t>
   </si>
   <si>
     <t>0: Never</t>
@@ -2828,10 +2882,10 @@
         <v>1</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="I2">
         <f>F2*VALUE(LEFT(H2, FIND(":", H2)-1))</f>
@@ -2860,10 +2914,10 @@
         <v>1</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I3">
         <f>F3*VALUE(LEFT(H3, FIND(":", H3)-1))</f>
@@ -2892,10 +2946,10 @@
         <v>1</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I4">
         <f>F4*VALUE(LEFT(H4, FIND(":", H4)-1))</f>
@@ -2924,10 +2978,10 @@
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I5">
         <f>F5*VALUE(LEFT(H5, FIND(":", H5)-1))</f>
@@ -2956,10 +3010,10 @@
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I6">
         <f>F6*VALUE(LEFT(H6, FIND(":", H6)-1))</f>
@@ -2990,7 +3044,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I7">
         <f>F7*VALUE(LEFT(H7, FIND(":", H7)-1))</f>
@@ -3019,7 +3073,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I8">
         <f>F8*VALUE(LEFT(H8, FIND(":", H8)-1))</f>
@@ -3048,7 +3102,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I9">
         <f>F9*VALUE(LEFT(H9, FIND(":", H9)-1))</f>
@@ -3077,10 +3131,10 @@
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I10">
         <f>F10*VALUE(LEFT(H10, FIND(":", H10)-1))</f>
@@ -3109,7 +3163,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I11">
         <f>F11*VALUE(LEFT(H11, FIND(":", H11)-1))</f>
@@ -3140,7 +3194,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I12">
         <f>F12*VALUE(LEFT(H12, FIND(":", H12)-1))</f>
@@ -3169,7 +3223,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I13">
         <f>F13*VALUE(LEFT(H13, FIND(":", H13)-1))</f>
@@ -3198,7 +3252,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I14">
         <f>F14*VALUE(LEFT(H14, FIND(":", H14)-1))</f>
@@ -3227,7 +3281,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I15">
         <f>F15*VALUE(LEFT(H15, FIND(":", H15)-1))</f>
@@ -3256,7 +3310,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I16">
         <f>F16*VALUE(LEFT(H16, FIND(":", H16)-1))</f>
@@ -3285,7 +3339,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I17">
         <f>F17*VALUE(LEFT(H17, FIND(":", H17)-1))</f>
@@ -3316,10 +3370,10 @@
         <v>1</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="I18">
         <f>F18*VALUE(LEFT(H18, FIND(":", H18)-1))</f>
@@ -3348,10 +3402,10 @@
         <v>1</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="I19">
         <f>F19*VALUE(LEFT(H19, FIND(":", H19)-1))</f>
@@ -3380,10 +3434,10 @@
         <v>1</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="I20">
         <f>F20*VALUE(LEFT(H20, FIND(":", H20)-1))</f>
@@ -3412,10 +3466,10 @@
         <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I21">
         <f>F21*VALUE(LEFT(H21, FIND(":", H21)-1))</f>
@@ -3444,7 +3498,7 @@
         <v>1</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I22">
         <f>F22*VALUE(LEFT(H22, FIND(":", H22)-1))</f>
@@ -3475,10 +3529,10 @@
         <v>1</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I23">
         <f>F23*VALUE(LEFT(H23, FIND(":", H23)-1))</f>
@@ -3507,10 +3561,10 @@
         <v>1</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I24">
         <f>F24*VALUE(LEFT(H24, FIND(":", H24)-1))</f>
@@ -3539,10 +3593,10 @@
         <v>1</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I25">
         <f>F25*VALUE(LEFT(H25, FIND(":", H25)-1))</f>
@@ -3571,10 +3625,10 @@
         <v>1</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I26">
         <f>F26*VALUE(LEFT(H26, FIND(":", H26)-1))</f>
@@ -3603,10 +3657,10 @@
         <v>1</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I27">
         <f>F27*VALUE(LEFT(H27, FIND(":", H27)-1))</f>
@@ -3635,10 +3689,10 @@
         <v>1</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I28">
         <f>F28*VALUE(LEFT(H28, FIND(":", H28)-1))</f>
@@ -3669,7 +3723,7 @@
         <v>1</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I29">
         <f>F29*VALUE(LEFT(H29, FIND(":", H29)-1))</f>
@@ -3698,7 +3752,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I30">
         <f>F30*VALUE(LEFT(H30, FIND(":", H30)-1))</f>
@@ -3727,7 +3781,7 @@
         <v>1</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I31">
         <f>F31*VALUE(LEFT(H31, FIND(":", H31)-1))</f>
@@ -3756,7 +3810,7 @@
         <v>1</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I32">
         <f>F32*VALUE(LEFT(H32, FIND(":", H32)-1))</f>
@@ -3785,7 +3839,7 @@
         <v>1</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I33">
         <f>F33*VALUE(LEFT(H33, FIND(":", H33)-1))</f>
@@ -3814,7 +3868,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I34">
         <f>F34*VALUE(LEFT(H34, FIND(":", H34)-1))</f>
@@ -3845,7 +3899,7 @@
         <v>1</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="I35">
         <f>F35*VALUE(LEFT(H35, FIND(":", H35)-1))</f>
@@ -3874,10 +3928,10 @@
         <v>1</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I36">
         <f>F36*VALUE(LEFT(H36, FIND(":", H36)-1))</f>
@@ -3906,10 +3960,10 @@
         <v>1</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I37">
         <f>F37*VALUE(LEFT(H37, FIND(":", H37)-1))</f>
@@ -3938,10 +3992,10 @@
         <v>1</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I38">
         <f>F38*VALUE(LEFT(H38, FIND(":", H38)-1))</f>
@@ -3974,7 +4028,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="I39">
         <f>F39*VALUE(LEFT(H39, FIND(":", H39)-1))</f>
@@ -4003,10 +4057,10 @@
         <v>1</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I40">
         <f>F40*VALUE(LEFT(H40, FIND(":", H40)-1))</f>
@@ -4035,7 +4089,7 @@
         <v>1</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="I41">
         <f>F41*VALUE(LEFT(H41, FIND(":", H41)-1))</f>
@@ -4064,10 +4118,10 @@
         <v>1</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I42">
         <f>F42*VALUE(LEFT(H42, FIND(":", H42)-1))</f>
@@ -4096,10 +4150,10 @@
         <v>1</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I43">
         <f>F43*VALUE(LEFT(H43, FIND(":", H43)-1))</f>
@@ -4128,7 +4182,7 @@
         <v>1</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I44">
         <f>F44*VALUE(LEFT(H44, FIND(":", H44)-1))</f>
@@ -4157,7 +4211,7 @@
         <v>1</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I45">
         <f>F45*VALUE(LEFT(H45, FIND(":", H45)-1))</f>
@@ -4186,7 +4240,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I46">
         <f>F46*VALUE(LEFT(H46, FIND(":", H46)-1))</f>
@@ -4215,10 +4269,10 @@
         <v>1</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I47">
         <f>F47*VALUE(LEFT(H47, FIND(":", H47)-1))</f>
@@ -4247,7 +4301,7 @@
         <v>1</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I48">
         <f>F48*VALUE(LEFT(H48, FIND(":", H48)-1))</f>
@@ -4276,7 +4330,7 @@
         <v>1</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I49">
         <f>F49*VALUE(LEFT(H49, FIND(":", H49)-1))</f>
@@ -4305,7 +4359,7 @@
         <v>1</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I50">
         <f>F50*VALUE(LEFT(H50, FIND(":", H50)-1))</f>
@@ -4336,7 +4390,7 @@
         <v>1</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="I51">
         <f>F51*VALUE(LEFT(H51, FIND(":", H51)-1))</f>
@@ -4365,7 +4419,7 @@
         <v>1</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I52">
         <f>F52*VALUE(LEFT(H52, FIND(":", H52)-1))</f>
@@ -4394,7 +4448,7 @@
         <v>1</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I53">
         <f>F53*VALUE(LEFT(H53, FIND(":", H53)-1))</f>
@@ -4423,7 +4477,7 @@
         <v>1</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I54">
         <f>F54*VALUE(LEFT(H54, FIND(":", H54)-1))</f>
@@ -4452,7 +4506,7 @@
         <v>1</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I55">
         <f>F55*VALUE(LEFT(H55, FIND(":", H55)-1))</f>
@@ -4481,7 +4535,7 @@
         <v>1</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I56">
         <f>F56*VALUE(LEFT(H56, FIND(":", H56)-1))</f>
@@ -4512,7 +4566,7 @@
         <v>1</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I57">
         <f>F57*VALUE(LEFT(H57, FIND(":", H57)-1))</f>
@@ -4541,7 +4595,7 @@
         <v>1</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I58">
         <f>F58*VALUE(LEFT(H58, FIND(":", H58)-1))</f>
@@ -4570,7 +4624,7 @@
         <v>1</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I59">
         <f>F59*VALUE(LEFT(H59, FIND(":", H59)-1))</f>
@@ -4599,7 +4653,7 @@
         <v>1</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I60">
         <f>F60*VALUE(LEFT(H60, FIND(":", H60)-1))</f>
@@ -4628,7 +4682,7 @@
         <v>1</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I61">
         <f>F61*VALUE(LEFT(H61, FIND(":", H61)-1))</f>
@@ -4657,10 +4711,10 @@
         <v>1</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I62">
         <f>F62*VALUE(LEFT(H62, FIND(":", H62)-1))</f>
@@ -4691,7 +4745,7 @@
         <v>1</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I63">
         <f>F63*VALUE(LEFT(H63, FIND(":", H63)-1))</f>
@@ -4720,7 +4774,7 @@
         <v>1</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="I64">
         <f>F64*VALUE(LEFT(H64, FIND(":", H64)-1))</f>
@@ -4749,7 +4803,7 @@
         <v>1</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="I65">
         <f>F65*VALUE(LEFT(H65, FIND(":", H65)-1))</f>
@@ -4778,7 +4832,7 @@
         <v>1</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I66">
         <f>F66*VALUE(LEFT(H66, FIND(":", H66)-1))</f>
@@ -4807,7 +4861,7 @@
         <v>1</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I67">
         <f>F67*VALUE(LEFT(H67, FIND(":", H67)-1))</f>
@@ -4836,7 +4890,7 @@
         <v>1</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I68">
         <f>F68*VALUE(LEFT(H68, FIND(":", H68)-1))</f>
@@ -4867,10 +4921,10 @@
         <v>1</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I69">
         <f>F69*VALUE(LEFT(H69, FIND(":", H69)-1))</f>
@@ -4899,10 +4953,10 @@
         <v>1</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="I70">
         <f>F70*VALUE(LEFT(H70, FIND(":", H70)-1))</f>
@@ -4931,10 +4985,10 @@
         <v>1</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I71">
         <f>F71*VALUE(LEFT(H71, FIND(":", H71)-1))</f>
@@ -4963,10 +5017,10 @@
         <v>1</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="I72">
         <f>F72*VALUE(LEFT(H72, FIND(":", H72)-1))</f>
@@ -4995,10 +5049,10 @@
         <v>1</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="I73">
         <f>F73*VALUE(LEFT(H73, FIND(":", H73)-1))</f>
@@ -5027,10 +5081,10 @@
         <v>1</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I74">
         <f>F74*VALUE(LEFT(H74, FIND(":", H74)-1))</f>
@@ -5059,7 +5113,7 @@
         <v>1</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I75">
         <f>F75*VALUE(LEFT(H75, FIND(":", H75)-1))</f>
@@ -5090,10 +5144,10 @@
         <v>1</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I76">
         <f>F76*VALUE(LEFT(H76, FIND(":", H76)-1))</f>
@@ -5122,10 +5176,10 @@
         <v>1</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I77">
         <f>F77*VALUE(LEFT(H77, FIND(":", H77)-1))</f>
@@ -5154,7 +5208,7 @@
         <v>1</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="I78">
         <f>F78*VALUE(LEFT(H78, FIND(":", H78)-1))</f>
@@ -5182,8 +5236,11 @@
       <c r="F79">
         <v>1</v>
       </c>
+      <c r="G79" s="1" t="s">
+        <v>348</v>
+      </c>
       <c r="H79" s="1" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="I79">
         <f>F79*VALUE(LEFT(H79, FIND(":", H79)-1))</f>
@@ -5211,8 +5268,11 @@
       <c r="F80">
         <v>1</v>
       </c>
+      <c r="G80" s="1" t="s">
+        <v>349</v>
+      </c>
       <c r="H80" s="1" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="I80">
         <f>F80*VALUE(LEFT(H80, FIND(":", H80)-1))</f>
@@ -5241,10 +5301,10 @@
         <v>1</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I81">
         <f>F81*VALUE(LEFT(H81, FIND(":", H81)-1))</f>
@@ -5272,8 +5332,11 @@
       <c r="F82">
         <v>1</v>
       </c>
+      <c r="G82" s="1" t="s">
+        <v>351</v>
+      </c>
       <c r="H82" s="1" t="s">
-        <v>401</v>
+        <v>416</v>
       </c>
       <c r="I82">
         <f>F82*VALUE(LEFT(H82, FIND(":", H82)-1))</f>
@@ -5304,7 +5367,7 @@
         <v>1</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I83">
         <f>F83*VALUE(LEFT(H83, FIND(":", H83)-1))</f>
@@ -5333,7 +5396,7 @@
         <v>1</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I84">
         <f>F84*VALUE(LEFT(H84, FIND(":", H84)-1))</f>
@@ -5362,7 +5425,7 @@
         <v>1</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I85">
         <f>F85*VALUE(LEFT(H85, FIND(":", H85)-1))</f>
@@ -5391,7 +5454,7 @@
         <v>1</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="I86">
         <f>F86*VALUE(LEFT(H86, FIND(":", H86)-1))</f>
@@ -5420,7 +5483,7 @@
         <v>1</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I87">
         <f>F87*VALUE(LEFT(H87, FIND(":", H87)-1))</f>
@@ -5449,10 +5512,10 @@
         <v>1</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I88">
         <f>F88*VALUE(LEFT(H88, FIND(":", H88)-1))</f>
@@ -5481,10 +5544,10 @@
         <v>1</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I89">
         <f>F89*VALUE(LEFT(H89, FIND(":", H89)-1))</f>
@@ -5513,7 +5576,7 @@
         <v>1</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I90">
         <f>F90*VALUE(LEFT(H90, FIND(":", H90)-1))</f>
@@ -5542,7 +5605,7 @@
         <v>1</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="I91">
         <f>F91*VALUE(LEFT(H91, FIND(":", H91)-1))</f>
@@ -5573,7 +5636,7 @@
         <v>1</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I92">
         <f>F92*VALUE(LEFT(H92, FIND(":", H92)-1))</f>
@@ -5602,10 +5665,10 @@
         <v>1</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I93">
         <f>F93*VALUE(LEFT(H93, FIND(":", H93)-1))</f>
@@ -5634,10 +5697,10 @@
         <v>1</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I94">
         <f>F94*VALUE(LEFT(H94, FIND(":", H94)-1))</f>
@@ -5666,7 +5729,7 @@
         <v>1</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I95">
         <f>F95*VALUE(LEFT(H95, FIND(":", H95)-1))</f>
@@ -5695,7 +5758,7 @@
         <v>1</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="I96">
         <f>F96*VALUE(LEFT(H96, FIND(":", H96)-1))</f>
@@ -5724,7 +5787,7 @@
         <v>1</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I97">
         <f>F97*VALUE(LEFT(H97, FIND(":", H97)-1))</f>
@@ -5753,7 +5816,7 @@
         <v>1</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I98">
         <f>F98*VALUE(LEFT(H98, FIND(":", H98)-1))</f>
@@ -5786,7 +5849,7 @@
         <v>1</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I99">
         <f>F99*VALUE(LEFT(H99, FIND(":", H99)-1))</f>
@@ -5815,7 +5878,7 @@
         <v>1</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I100">
         <f>F100*VALUE(LEFT(H100, FIND(":", H100)-1))</f>
@@ -5844,7 +5907,7 @@
         <v>1</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I101">
         <f>F101*VALUE(LEFT(H101, FIND(":", H101)-1))</f>
@@ -5873,7 +5936,7 @@
         <v>1</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I102">
         <f>F102*VALUE(LEFT(H102, FIND(":", H102)-1))</f>
@@ -5902,7 +5965,7 @@
         <v>1</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="I103">
         <f>F103*VALUE(LEFT(H103, FIND(":", H103)-1))</f>
@@ -5931,7 +5994,7 @@
         <v>1</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I104">
         <f>F104*VALUE(LEFT(H104, FIND(":", H104)-1))</f>
@@ -5962,7 +6025,7 @@
         <v>1</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="I105">
         <f>F105*VALUE(LEFT(H105, FIND(":", H105)-1))</f>
@@ -5991,7 +6054,7 @@
         <v>1</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="I106">
         <f>F106*VALUE(LEFT(H106, FIND(":", H106)-1))</f>
@@ -6020,7 +6083,7 @@
         <v>1</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I107">
         <f>F107*VALUE(LEFT(H107, FIND(":", H107)-1))</f>
@@ -6049,7 +6112,7 @@
         <v>1</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I108">
         <f>F108*VALUE(LEFT(H108, FIND(":", H108)-1))</f>
@@ -6078,7 +6141,7 @@
         <v>1</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I109">
         <f>F109*VALUE(LEFT(H109, FIND(":", H109)-1))</f>
@@ -6107,7 +6170,7 @@
         <v>1</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I110">
         <f>F110*VALUE(LEFT(H110, FIND(":", H110)-1))</f>
@@ -6138,7 +6201,7 @@
         <v>1</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I111">
         <f>F111*VALUE(LEFT(H111, FIND(":", H111)-1))</f>
@@ -6161,16 +6224,16 @@
         <v>286</v>
       </c>
       <c r="E112" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="F112">
         <v>1</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I112">
         <f>F112*VALUE(LEFT(H112, FIND(":", H112)-1))</f>
@@ -6193,13 +6256,13 @@
         <v>287</v>
       </c>
       <c r="E113" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="F113">
         <v>1</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="I113">
         <f>F113*VALUE(LEFT(H113, FIND(":", H113)-1))</f>
@@ -6228,10 +6291,10 @@
         <v>1</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="I114">
         <f>F114*VALUE(LEFT(H114, FIND(":", H114)-1))</f>
@@ -6260,7 +6323,7 @@
         <v>1</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="I115">
         <f>F115*VALUE(LEFT(H115, FIND(":", H115)-1))</f>
@@ -6289,10 +6352,10 @@
         <v>1</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I116">
         <f>F116*VALUE(LEFT(H116, FIND(":", H116)-1))</f>
@@ -6323,10 +6386,10 @@
         <v>1</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I117">
         <f>F117*VALUE(LEFT(H117, FIND(":", H117)-1))</f>
@@ -6355,10 +6418,10 @@
         <v>1</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I118">
         <f>F118*VALUE(LEFT(H118, FIND(":", H118)-1))</f>
@@ -6387,10 +6450,10 @@
         <v>1</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I119">
         <f>F119*VALUE(LEFT(H119, FIND(":", H119)-1))</f>
@@ -6419,10 +6482,10 @@
         <v>1</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I120">
         <f>F120*VALUE(LEFT(H120, FIND(":", H120)-1))</f>
@@ -6451,10 +6514,10 @@
         <v>1</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I121">
         <f>F121*VALUE(LEFT(H121, FIND(":", H121)-1))</f>
@@ -6483,7 +6546,7 @@
         <v>1</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="I122">
         <f>F122*VALUE(LEFT(H122, FIND(":", H122)-1))</f>
@@ -6512,10 +6575,10 @@
         <v>1</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I123">
         <f>F123*VALUE(LEFT(H123, FIND(":", H123)-1))</f>
@@ -6546,10 +6609,10 @@
         <v>1</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I124">
         <f>F124*VALUE(LEFT(H124, FIND(":", H124)-1))</f>
@@ -6578,10 +6641,10 @@
         <v>1</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I125">
         <f>F125*VALUE(LEFT(H125, FIND(":", H125)-1))</f>
@@ -6610,10 +6673,10 @@
         <v>1</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I126">
         <f>F126*VALUE(LEFT(H126, FIND(":", H126)-1))</f>
@@ -6642,10 +6705,10 @@
         <v>1</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I127">
         <f>F127*VALUE(LEFT(H127, FIND(":", H127)-1))</f>
@@ -6674,10 +6737,10 @@
         <v>1</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I128">
         <f>F128*VALUE(LEFT(H128, FIND(":", H128)-1))</f>
@@ -6706,7 +6769,7 @@
         <v>1</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="I129">
         <f>F129*VALUE(LEFT(H129, FIND(":", H129)-1))</f>
@@ -6739,7 +6802,7 @@
         <v>1</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I130">
         <f>F130*VALUE(LEFT(H130, FIND(":", H130)-1))</f>
@@ -6768,7 +6831,7 @@
         <v>1</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I131">
         <f>F131*VALUE(LEFT(H131, FIND(":", H131)-1))</f>
@@ -6797,7 +6860,7 @@
         <v>1</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I132">
         <f>F132*VALUE(LEFT(H132, FIND(":", H132)-1))</f>
@@ -6826,7 +6889,7 @@
         <v>1</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="I133">
         <f>F133*VALUE(LEFT(H133, FIND(":", H133)-1))</f>
@@ -6855,7 +6918,7 @@
         <v>1</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I134">
         <f>F134*VALUE(LEFT(H134, FIND(":", H134)-1))</f>
@@ -7129,16 +7192,16 @@
       <formula1>"0: No alerting to any owners,1: Alerting in at least one owner,3: Alerting to some owners [&gt;20%],6: Alerting to most owners [&gt;60%],10: Alerting to all owners [100%]"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H79">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H80">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: item 1 completed,4: items 1-2 completed,6: items 1-3 completed,8: items 1-4 completed,10: items 1-5 completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H81">
       <formula1>"0: No items completed,2: 1 item completed,3: 2 items completed,4: 3 items completed,5: 4 items completed,7: 5 items completed,8: 6 items completed,9: 7 items completed,10: 8 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H82">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: Low Maturity. Score Range (0-14),4: Developing. Score Range (15-30),7: Established. Score Range (31-42),10: Optimizing. Score Range (43-50)"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H83">
       <formula1>"0: Not done,10: Completed"</formula1>

--- a/assessments/FinOps++/assessment.xlsx
+++ b/assessments/FinOps++/assessment.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="432">
   <si>
     <t>Sum of Weights</t>
   </si>
@@ -403,6 +403,9 @@
     <t>Define Data Granularity &amp; Frequency</t>
   </si>
   <si>
+    <t>Define Data Ingestion Requirements</t>
+  </si>
+  <si>
     <t>Document Normalization Rules</t>
   </si>
   <si>
@@ -415,9 +418,6 @@
     <t>Optimize Pipelines for Timeliness</t>
   </si>
   <si>
-    <t>Define Data Ingestion Requirements</t>
-  </si>
-  <si>
     <t>Gather Requirements &amp; Define KPIs</t>
   </si>
   <si>
@@ -532,7 +532,7 @@
     <t>Communicate Unit Cost Wins</t>
   </si>
   <si>
-    <t>Draft Cloud Financial Policies</t>
+    <t>Define Technology Financial Policies</t>
   </si>
   <si>
     <t>Publish Guidelines &amp; Guardrails</t>
@@ -544,7 +544,7 @@
     <t>Monitor Compliance &amp; Report Breaches</t>
   </si>
   <si>
-    <t>Iterate Policies Based on Feedback</t>
+    <t>Iterate Policies on Outcomes &amp; Risk</t>
   </si>
   <si>
     <t>113</t>
@@ -802,6 +802,9 @@
     <t>004</t>
   </si>
   <si>
+    <t>135</t>
+  </si>
+  <si>
     <t>005</t>
   </si>
   <si>
@@ -812,9 +815,6 @@
   </si>
   <si>
     <t>008</t>
-  </si>
-  <si>
-    <t>135</t>
   </si>
   <si>
     <t>016</t>
@@ -1147,6 +1147,56 @@
 10*Ceil(x/3)</t>
   </si>
   <si>
+    <t>* Weighted sum
+  Effective savings rate (score x4),
+  Commitment coverage (score x3),
+  Purchase cadence (score x2),
+  Purchase criteria (score x1).
+  Max raw (50)
+* Effective savings rate achieved on the portfolio, net of unused commitment, scored as a share of
+  the rate the portfolio's own commitment terms make available
+  (expected rate = 25% + 7.5% x (weighted-average commitment term in years - 1), so one-year terms
+  expect 25%, two-year 32.5%, and three-year 40%)
+  (0=Not measured, 1&lt;50%, 2=50-69%, 3=70-84%, 4=85-99%, 5=100% or higher)
+* Share of eligible usage covered by a commitment over the review period
+  (0=Not measured, 1&lt;25%, 2=25-49%, 3=50-69%, 4=70-84%, 5=85% or higher)
+* How often commitments are purchased rather than left to renew in bulk
+  (0=None purchased, 1=One-off, 2=Annual, 3=Quarterly, 4=Monthly or more often,
+  5=Purchases triggered automatically by coverage and utilization reporting)
+* Which numeric tests a purchase must pass before approval
+  (0=None, 1=A savings target stated informally, 2=Savings per dollar of commitment recorded,
+  3=Break-even window also recorded, 4=Expected usage life recorded and the term justified against it,
+  5=All three applied to each decision and the portfolio rebalanced against realized usage)
+* Output Range (0-50)</t>
+  </si>
+  <si>
+    <t>Measured over: every commitment held during the review period, and every commitment expiring in it.
+A portfolio is small enough to enumerate, so items are assessed against each commitment rather than as
+a coverage rate.
+* Return reported (the return on each commitment is reported in currency or as an effective savings
+  rate)
+* Coverage reported (the share of eligible usage covered by commitments is reported for the period)
+* Decline alerting (an alert fires to a named recipient when utilization falls below the level
+  recorded in the commitment strategy)
+* Expiration register (every commitment carries an expiry date and a named owner)
+* Advance notice (owners of expiring commitments are notified at least one full purchase cycle before
+  expiry)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>Measured over: every commitment held during the review period. These are few enough to enumerate, so
+items are assessed against each commitment rather than as a coverage rate.
+* Amortized view published (commitment cost is reported spread across the commitment term rather than
+  landing in the month it is invoiced)
+* Allocation rule documented (how the upfront amount and the remaining term charges reach the teams
+  whose usage the commitment covers, including the treatment of unused commitment)
+* Benefit visible to the team (a team can see the discounted rate it received, not only an aggregate
+  saving for the organization)
+* Unallocated commitment cost reported (the amount no team receives is reported in currency for the
+  period)
+10*Ceil(x/4)</t>
+  </si>
+  <si>
     <t>* Process for evaluating spot periodically
 * Tag for date last reviewed
 * New deployments get reviewed beforehand
@@ -1184,6 +1234,16 @@
 * Remove untagged resources after time threshold
 * Block deployments without proper tags
 * Automatically tag based on CI/CD creator and team
+10*Ceil(x/4)</t>
+  </si>
+  <si>
+    <t>Measured over: every change to metadata, hierarchy, or shared cost rules made during the review period.
+Changes are few enough to enumerate, so items are assessed against each one rather than as a coverage
+rate.
+* Recurring review (the allocation strategy is reviewed on a published cadence with a named owner)
+* Change record (every change carries a rationale and an effective date)
+* Advance notice (every change reaches affected resource and budget owners before the effective date)
+* Carried gaps (each review records the gaps it did not close, and the next review lists them)
 10*Ceil(x/4)</t>
   </si>
   <si>
@@ -1297,6 +1357,15 @@
 10*Ceil(x/4)</t>
   </si>
   <si>
+    <t>* Purpose recorded (the decisions the forecast exists to support, and the stakeholders who agreed them)
+* Technique recorded (static, trend-based, or driver-based, stated for each organizational level the
+  forecast is produced at)
+* Cadence requirement recorded (when a forecast is due, and how often it is expected to be updated)
+* Horizon recorded (how far forward the forecast reaches, how much history feeds it, and at what
+  granularity)
+10*Ceil(x/4)</t>
+  </si>
+  <si>
     <t>* Collect data based on existing patterns observed in spend
 * Conduct proactive investigations and interviews with teams
 * Gather existing self reporting by the business and/or teams
@@ -1396,6 +1465,61 @@
 10*Ceil(x/4)</t>
   </si>
   <si>
+    <t>Measured over: every policy in force during the review period. A policy set is small enough to
+enumerate, so items are assessed against each policy rather than as a coverage rate.
+* Policy register (policies in force are listed in one place, each with a named owner and an effective
+  date)
+* Risk named (each policy records the financial risk it exists to reduce)
+* Scope stated (each policy records which FinOps Scopes and technology categories it applies to)
+* Approval recorded (each policy records who approved it and at what level of authority)
+* Next review dated (each policy carries the date by which it is reviewed again)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>* Weighted sum
+  Guardrail coverage (score x4),
+  Enforcement mode (score x3),
+  Guideline publication (score x2),
+  Exception path (score x1).
+  Max raw (50)
+* Share of routine technology decisions that pass through an automated guardrail
+  (0=Not measured, 1&lt;20%, 2=20-39%, 3=40-59%, 4=60-79%, 5=80% or higher)
+* How a guardrail responds when a decision breaches policy
+  (0=No guardrails, 1=Reported after the fact, 2=Warns the requester, 3=Warns and notifies the owner,
+  4=Blocks the breach with an override path, 5=Blocks and remediates the drift automatically)
+* Where guidelines are published and who can reach them
+  (0=Unpublished, 1=Shared on request, 2=Published to the FinOps team,
+  3=Published to the personas each guideline binds, 4=Reachable from the tools where decisions are
+  made, 5=Versioned, with changes announced to the personas they bind)
+* How an exception is requested and bounded
+  (0=No exception path, 1=Granted informally, 2=Requested and recorded, 3=Approved by a named role,
+  4=Carries an expiry date, 5=Reviewed at expiry and either renewed with rationale or withdrawn)
+* Output Range (0-50)</t>
+  </si>
+  <si>
+    <t>Measured over: every policy in force during the review period, and the personas each one binds.
+* Expectations delivered (each policy has been communicated to the personas it binds, not only to the
+  FinOps team)
+* Exception path communicated (the personas a policy binds know how to request an exception, who
+  decides, and how long one lasts)
+* Risk acceptance recorded (where a policy is waived or a breach is tolerated, the leader accepting
+  that risk is named in the record)
+* Handover covered (a new owner receives the policies that bind their scope when they take ownership)
+10*Ceil(x/4)</t>
+  </si>
+  <si>
+    <t>Measured over: every policy in force during the review period, and every change made to one.
+* Review cadence published (the policy set is reviewed on a stated cadence with a named owner)
+* Outcome data feeds the review (adherence rate, breach counts, and guardrail false positives are
+  inputs to it rather than reported separately)
+* Feedback path open (the personas a policy binds can raise an issue through a stated route, and
+  those issues reach the review)
+* Change recorded (each policy change records its rationale and effective date)
+* Retirement path exists (a policy can be withdrawn through a stated route, and each review records
+  which policies were kept, amended, or withdrawn)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
     <t>[{'Score': 0, 'Condition': '0 items completed'}, {'Score': 3, 'Condition': '1 item completed'}, {'Score': 5, 'Condition': '2 items completed'}, {'Score': 8, 'Condition': '3 items completed'}, {'Score': 10, 'Condition': '4 items completed'}]</t>
   </si>
   <si>
@@ -1450,6 +1574,9 @@
     <t>[{'Score': 0, 'Condition': 'Not done'}, {'Score': 10, 'Condition': 'Policy in place and published'}]</t>
   </si>
   <si>
+    <t>[{'Score': 0, 'Condition': 'Low Maturity, Score Range (0-14)'}, {'Score': 4, 'Condition': 'Developing, Score Range (15-30)'}, {'Score': 7, 'Condition': 'Established, Score Range (31-42)'}, {'Score': 10, 'Condition': 'Optimizing, Score Range (43-50)'}]</t>
+  </si>
+  <si>
     <t>[{'Score': 0, 'Condition': 'No teardown/shutdown policy'}, {'Score': 3, 'Condition': 'Published policy'}, {'Score': 6, 'Condition': 'Classification tagged or otherwise identifiable'}, {'Score': 10, 'Condition': 'Enforced Policy with tagged/identifiable classifications'}]</t>
   </si>
   <si>
@@ -1468,9 +1595,6 @@
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': '1 item completed'}, {'Score': 3, 'Condition': '2 items completed'}, {'Score': 4, 'Condition': '3 items completed'}, {'Score': 5, 'Condition': '4 items completed'}, {'Score': 7, 'Condition': '5 items completed'}, {'Score': 8, 'Condition': '6 items completed'}, {'Score': 9, 'Condition': '7 items completed'}, {'Score': 10, 'Condition': '8 items completed'}]</t>
   </si>
   <si>
-    <t>[{'Score': 0, 'Condition': 'Low Maturity, Score Range (0-14)'}, {'Score': 4, 'Condition': 'Developing, Score Range (15-30)'}, {'Score': 7, 'Condition': 'Established, Score Range (31-42)'}, {'Score': 10, 'Condition': 'Optimizing, Score Range (43-50)'}]</t>
-  </si>
-  <si>
     <t>[{'Score': 0, 'Condition': 'Never'}, {'Score': 1, 'Condition': 'Monthly or greater'}, {'Score': 2, 'Condition': 'More than a week'}, {'Score': 3, 'Condition': '7 days'}, {'Score': 4, 'Condition': '5 days'}, {'Score': 6, 'Condition': '2 days'}, {'Score': 8, 'Condition': '1 day'}, {'Score': 10, 'Condition': 'Instant'}]</t>
   </si>
   <si>
@@ -1528,13 +1652,13 @@
     <t>0: 0%</t>
   </si>
   <si>
+    <t>0: Low Maturity. Score Range (0-14)</t>
+  </si>
+  <si>
     <t>0: No teardown/shutdown policy</t>
   </si>
   <si>
     <t>0: No alerting to any owners</t>
-  </si>
-  <si>
-    <t>0: Low Maturity. Score Range (0-14)</t>
   </si>
   <si>
     <t>0: Never</t>
@@ -2885,7 +3009,7 @@
         <v>316</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="I2">
         <f>F2*VALUE(LEFT(H2, FIND(":", H2)-1))</f>
@@ -2917,7 +3041,7 @@
         <v>317</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I3">
         <f>F3*VALUE(LEFT(H3, FIND(":", H3)-1))</f>
@@ -2949,7 +3073,7 @@
         <v>318</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I4">
         <f>F4*VALUE(LEFT(H4, FIND(":", H4)-1))</f>
@@ -2981,7 +3105,7 @@
         <v>319</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I5">
         <f>F5*VALUE(LEFT(H5, FIND(":", H5)-1))</f>
@@ -3013,7 +3137,7 @@
         <v>320</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I6">
         <f>F6*VALUE(LEFT(H6, FIND(":", H6)-1))</f>
@@ -3044,7 +3168,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I7">
         <f>F7*VALUE(LEFT(H7, FIND(":", H7)-1))</f>
@@ -3073,7 +3197,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I8">
         <f>F8*VALUE(LEFT(H8, FIND(":", H8)-1))</f>
@@ -3102,7 +3226,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I9">
         <f>F9*VALUE(LEFT(H9, FIND(":", H9)-1))</f>
@@ -3134,7 +3258,7 @@
         <v>321</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I10">
         <f>F10*VALUE(LEFT(H10, FIND(":", H10)-1))</f>
@@ -3163,7 +3287,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I11">
         <f>F11*VALUE(LEFT(H11, FIND(":", H11)-1))</f>
@@ -3194,7 +3318,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I12">
         <f>F12*VALUE(LEFT(H12, FIND(":", H12)-1))</f>
@@ -3223,7 +3347,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I13">
         <f>F13*VALUE(LEFT(H13, FIND(":", H13)-1))</f>
@@ -3252,7 +3376,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I14">
         <f>F14*VALUE(LEFT(H14, FIND(":", H14)-1))</f>
@@ -3281,7 +3405,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I15">
         <f>F15*VALUE(LEFT(H15, FIND(":", H15)-1))</f>
@@ -3310,7 +3434,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I16">
         <f>F16*VALUE(LEFT(H16, FIND(":", H16)-1))</f>
@@ -3339,7 +3463,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I17">
         <f>F17*VALUE(LEFT(H17, FIND(":", H17)-1))</f>
@@ -3373,7 +3497,7 @@
         <v>322</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="I18">
         <f>F18*VALUE(LEFT(H18, FIND(":", H18)-1))</f>
@@ -3405,7 +3529,7 @@
         <v>323</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="I19">
         <f>F19*VALUE(LEFT(H19, FIND(":", H19)-1))</f>
@@ -3437,7 +3561,7 @@
         <v>324</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="I20">
         <f>F20*VALUE(LEFT(H20, FIND(":", H20)-1))</f>
@@ -3469,7 +3593,7 @@
         <v>325</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I21">
         <f>F21*VALUE(LEFT(H21, FIND(":", H21)-1))</f>
@@ -3498,7 +3622,7 @@
         <v>1</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I22">
         <f>F22*VALUE(LEFT(H22, FIND(":", H22)-1))</f>
@@ -3532,7 +3656,7 @@
         <v>326</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I23">
         <f>F23*VALUE(LEFT(H23, FIND(":", H23)-1))</f>
@@ -3564,7 +3688,7 @@
         <v>327</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I24">
         <f>F24*VALUE(LEFT(H24, FIND(":", H24)-1))</f>
@@ -3596,7 +3720,7 @@
         <v>328</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I25">
         <f>F25*VALUE(LEFT(H25, FIND(":", H25)-1))</f>
@@ -3628,7 +3752,7 @@
         <v>329</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I26">
         <f>F26*VALUE(LEFT(H26, FIND(":", H26)-1))</f>
@@ -3660,7 +3784,7 @@
         <v>330</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I27">
         <f>F27*VALUE(LEFT(H27, FIND(":", H27)-1))</f>
@@ -3692,7 +3816,7 @@
         <v>331</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I28">
         <f>F28*VALUE(LEFT(H28, FIND(":", H28)-1))</f>
@@ -3723,7 +3847,7 @@
         <v>1</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I29">
         <f>F29*VALUE(LEFT(H29, FIND(":", H29)-1))</f>
@@ -3752,7 +3876,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I30">
         <f>F30*VALUE(LEFT(H30, FIND(":", H30)-1))</f>
@@ -3781,7 +3905,7 @@
         <v>1</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I31">
         <f>F31*VALUE(LEFT(H31, FIND(":", H31)-1))</f>
@@ -3810,7 +3934,7 @@
         <v>1</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I32">
         <f>F32*VALUE(LEFT(H32, FIND(":", H32)-1))</f>
@@ -3839,7 +3963,7 @@
         <v>1</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I33">
         <f>F33*VALUE(LEFT(H33, FIND(":", H33)-1))</f>
@@ -3868,7 +3992,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I34">
         <f>F34*VALUE(LEFT(H34, FIND(":", H34)-1))</f>
@@ -3899,7 +4023,7 @@
         <v>1</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="I35">
         <f>F35*VALUE(LEFT(H35, FIND(":", H35)-1))</f>
@@ -3931,7 +4055,7 @@
         <v>332</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I36">
         <f>F36*VALUE(LEFT(H36, FIND(":", H36)-1))</f>
@@ -3963,7 +4087,7 @@
         <v>333</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I37">
         <f>F37*VALUE(LEFT(H37, FIND(":", H37)-1))</f>
@@ -3995,7 +4119,7 @@
         <v>334</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I38">
         <f>F38*VALUE(LEFT(H38, FIND(":", H38)-1))</f>
@@ -4028,7 +4152,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="I39">
         <f>F39*VALUE(LEFT(H39, FIND(":", H39)-1))</f>
@@ -4060,7 +4184,7 @@
         <v>335</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I40">
         <f>F40*VALUE(LEFT(H40, FIND(":", H40)-1))</f>
@@ -4089,7 +4213,7 @@
         <v>1</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="I41">
         <f>F41*VALUE(LEFT(H41, FIND(":", H41)-1))</f>
@@ -4121,7 +4245,7 @@
         <v>336</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I42">
         <f>F42*VALUE(LEFT(H42, FIND(":", H42)-1))</f>
@@ -4153,7 +4277,7 @@
         <v>337</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I43">
         <f>F43*VALUE(LEFT(H43, FIND(":", H43)-1))</f>
@@ -4182,7 +4306,7 @@
         <v>1</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I44">
         <f>F44*VALUE(LEFT(H44, FIND(":", H44)-1))</f>
@@ -4211,7 +4335,7 @@
         <v>1</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I45">
         <f>F45*VALUE(LEFT(H45, FIND(":", H45)-1))</f>
@@ -4240,7 +4364,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I46">
         <f>F46*VALUE(LEFT(H46, FIND(":", H46)-1))</f>
@@ -4272,7 +4396,7 @@
         <v>338</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I47">
         <f>F47*VALUE(LEFT(H47, FIND(":", H47)-1))</f>
@@ -4301,7 +4425,7 @@
         <v>1</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I48">
         <f>F48*VALUE(LEFT(H48, FIND(":", H48)-1))</f>
@@ -4330,7 +4454,7 @@
         <v>1</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I49">
         <f>F49*VALUE(LEFT(H49, FIND(":", H49)-1))</f>
@@ -4359,7 +4483,7 @@
         <v>1</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I50">
         <f>F50*VALUE(LEFT(H50, FIND(":", H50)-1))</f>
@@ -4390,7 +4514,7 @@
         <v>1</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="I51">
         <f>F51*VALUE(LEFT(H51, FIND(":", H51)-1))</f>
@@ -4419,7 +4543,7 @@
         <v>1</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I52">
         <f>F52*VALUE(LEFT(H52, FIND(":", H52)-1))</f>
@@ -4448,7 +4572,7 @@
         <v>1</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I53">
         <f>F53*VALUE(LEFT(H53, FIND(":", H53)-1))</f>
@@ -4477,7 +4601,7 @@
         <v>1</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I54">
         <f>F54*VALUE(LEFT(H54, FIND(":", H54)-1))</f>
@@ -4506,7 +4630,7 @@
         <v>1</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I55">
         <f>F55*VALUE(LEFT(H55, FIND(":", H55)-1))</f>
@@ -4535,7 +4659,7 @@
         <v>1</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I56">
         <f>F56*VALUE(LEFT(H56, FIND(":", H56)-1))</f>
@@ -4566,7 +4690,7 @@
         <v>1</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I57">
         <f>F57*VALUE(LEFT(H57, FIND(":", H57)-1))</f>
@@ -4595,7 +4719,7 @@
         <v>1</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I58">
         <f>F58*VALUE(LEFT(H58, FIND(":", H58)-1))</f>
@@ -4618,13 +4742,16 @@
         <v>233</v>
       </c>
       <c r="E59" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
+      <c r="G59" s="1" t="s">
+        <v>339</v>
+      </c>
       <c r="H59" s="1" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="I59">
         <f>F59*VALUE(LEFT(H59, FIND(":", H59)-1))</f>
@@ -4647,13 +4774,16 @@
         <v>234</v>
       </c>
       <c r="E60" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F60">
         <v>1</v>
       </c>
+      <c r="G60" s="1" t="s">
+        <v>340</v>
+      </c>
       <c r="H60" s="1" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="I60">
         <f>F60*VALUE(LEFT(H60, FIND(":", H60)-1))</f>
@@ -4676,13 +4806,16 @@
         <v>235</v>
       </c>
       <c r="E61" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
+      <c r="G61" s="1" t="s">
+        <v>341</v>
+      </c>
       <c r="H61" s="1" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="I61">
         <f>F61*VALUE(LEFT(H61, FIND(":", H61)-1))</f>
@@ -4711,10 +4844,10 @@
         <v>1</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I62">
         <f>F62*VALUE(LEFT(H62, FIND(":", H62)-1))</f>
@@ -4745,7 +4878,7 @@
         <v>1</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I63">
         <f>F63*VALUE(LEFT(H63, FIND(":", H63)-1))</f>
@@ -4774,7 +4907,7 @@
         <v>1</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="I64">
         <f>F64*VALUE(LEFT(H64, FIND(":", H64)-1))</f>
@@ -4803,7 +4936,7 @@
         <v>1</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="I65">
         <f>F65*VALUE(LEFT(H65, FIND(":", H65)-1))</f>
@@ -4832,7 +4965,7 @@
         <v>1</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I66">
         <f>F66*VALUE(LEFT(H66, FIND(":", H66)-1))</f>
@@ -4861,7 +4994,7 @@
         <v>1</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I67">
         <f>F67*VALUE(LEFT(H67, FIND(":", H67)-1))</f>
@@ -4890,7 +5023,7 @@
         <v>1</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I68">
         <f>F68*VALUE(LEFT(H68, FIND(":", H68)-1))</f>
@@ -4921,10 +5054,10 @@
         <v>1</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I69">
         <f>F69*VALUE(LEFT(H69, FIND(":", H69)-1))</f>
@@ -4953,10 +5086,10 @@
         <v>1</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="I70">
         <f>F70*VALUE(LEFT(H70, FIND(":", H70)-1))</f>
@@ -4985,10 +5118,10 @@
         <v>1</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I71">
         <f>F71*VALUE(LEFT(H71, FIND(":", H71)-1))</f>
@@ -5017,10 +5150,10 @@
         <v>1</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="I72">
         <f>F72*VALUE(LEFT(H72, FIND(":", H72)-1))</f>
@@ -5049,10 +5182,10 @@
         <v>1</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="I73">
         <f>F73*VALUE(LEFT(H73, FIND(":", H73)-1))</f>
@@ -5081,10 +5214,10 @@
         <v>1</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I74">
         <f>F74*VALUE(LEFT(H74, FIND(":", H74)-1))</f>
@@ -5107,13 +5240,16 @@
         <v>249</v>
       </c>
       <c r="E75" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F75">
         <v>1</v>
       </c>
+      <c r="G75" s="1" t="s">
+        <v>349</v>
+      </c>
       <c r="H75" s="1" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="I75">
         <f>F75*VALUE(LEFT(H75, FIND(":", H75)-1))</f>
@@ -5144,10 +5280,10 @@
         <v>1</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I76">
         <f>F76*VALUE(LEFT(H76, FIND(":", H76)-1))</f>
@@ -5176,10 +5312,10 @@
         <v>1</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I77">
         <f>F77*VALUE(LEFT(H77, FIND(":", H77)-1))</f>
@@ -5208,7 +5344,7 @@
         <v>1</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="I78">
         <f>F78*VALUE(LEFT(H78, FIND(":", H78)-1))</f>
@@ -5237,10 +5373,10 @@
         <v>1</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I79">
         <f>F79*VALUE(LEFT(H79, FIND(":", H79)-1))</f>
@@ -5269,10 +5405,10 @@
         <v>1</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I80">
         <f>F80*VALUE(LEFT(H80, FIND(":", H80)-1))</f>
@@ -5301,10 +5437,10 @@
         <v>1</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I81">
         <f>F81*VALUE(LEFT(H81, FIND(":", H81)-1))</f>
@@ -5333,10 +5469,10 @@
         <v>1</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="I82">
         <f>F82*VALUE(LEFT(H82, FIND(":", H82)-1))</f>
@@ -5367,7 +5503,7 @@
         <v>1</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I83">
         <f>F83*VALUE(LEFT(H83, FIND(":", H83)-1))</f>
@@ -5396,7 +5532,7 @@
         <v>1</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I84">
         <f>F84*VALUE(LEFT(H84, FIND(":", H84)-1))</f>
@@ -5425,7 +5561,7 @@
         <v>1</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I85">
         <f>F85*VALUE(LEFT(H85, FIND(":", H85)-1))</f>
@@ -5454,7 +5590,7 @@
         <v>1</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="I86">
         <f>F86*VALUE(LEFT(H86, FIND(":", H86)-1))</f>
@@ -5477,13 +5613,13 @@
         <v>261</v>
       </c>
       <c r="E87" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F87">
         <v>1</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="I87">
         <f>F87*VALUE(LEFT(H87, FIND(":", H87)-1))</f>
@@ -5506,16 +5642,13 @@
         <v>262</v>
       </c>
       <c r="E88" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F88">
         <v>1</v>
       </c>
-      <c r="G88" s="1" t="s">
-        <v>352</v>
-      </c>
       <c r="H88" s="1" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="I88">
         <f>F88*VALUE(LEFT(H88, FIND(":", H88)-1))</f>
@@ -5544,10 +5677,10 @@
         <v>1</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I89">
         <f>F89*VALUE(LEFT(H89, FIND(":", H89)-1))</f>
@@ -5570,13 +5703,16 @@
         <v>264</v>
       </c>
       <c r="E90" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F90">
         <v>1</v>
       </c>
+      <c r="G90" s="1" t="s">
+        <v>357</v>
+      </c>
       <c r="H90" s="1" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="I90">
         <f>F90*VALUE(LEFT(H90, FIND(":", H90)-1))</f>
@@ -5599,13 +5735,13 @@
         <v>265</v>
       </c>
       <c r="E91" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="F91">
         <v>1</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I91">
         <f>F91*VALUE(LEFT(H91, FIND(":", H91)-1))</f>
@@ -5636,7 +5772,7 @@
         <v>1</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I92">
         <f>F92*VALUE(LEFT(H92, FIND(":", H92)-1))</f>
@@ -5665,10 +5801,10 @@
         <v>1</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I93">
         <f>F93*VALUE(LEFT(H93, FIND(":", H93)-1))</f>
@@ -5697,10 +5833,10 @@
         <v>1</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I94">
         <f>F94*VALUE(LEFT(H94, FIND(":", H94)-1))</f>
@@ -5729,7 +5865,7 @@
         <v>1</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I95">
         <f>F95*VALUE(LEFT(H95, FIND(":", H95)-1))</f>
@@ -5758,7 +5894,7 @@
         <v>1</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="I96">
         <f>F96*VALUE(LEFT(H96, FIND(":", H96)-1))</f>
@@ -5787,7 +5923,7 @@
         <v>1</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I97">
         <f>F97*VALUE(LEFT(H97, FIND(":", H97)-1))</f>
@@ -5816,7 +5952,7 @@
         <v>1</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I98">
         <f>F98*VALUE(LEFT(H98, FIND(":", H98)-1))</f>
@@ -5849,7 +5985,7 @@
         <v>1</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I99">
         <f>F99*VALUE(LEFT(H99, FIND(":", H99)-1))</f>
@@ -5878,7 +6014,7 @@
         <v>1</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I100">
         <f>F100*VALUE(LEFT(H100, FIND(":", H100)-1))</f>
@@ -5907,7 +6043,7 @@
         <v>1</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I101">
         <f>F101*VALUE(LEFT(H101, FIND(":", H101)-1))</f>
@@ -5936,7 +6072,7 @@
         <v>1</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I102">
         <f>F102*VALUE(LEFT(H102, FIND(":", H102)-1))</f>
@@ -5965,7 +6101,7 @@
         <v>1</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="I103">
         <f>F103*VALUE(LEFT(H103, FIND(":", H103)-1))</f>
@@ -5994,7 +6130,7 @@
         <v>1</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I104">
         <f>F104*VALUE(LEFT(H104, FIND(":", H104)-1))</f>
@@ -6025,7 +6161,7 @@
         <v>1</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="I105">
         <f>F105*VALUE(LEFT(H105, FIND(":", H105)-1))</f>
@@ -6054,7 +6190,7 @@
         <v>1</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="I106">
         <f>F106*VALUE(LEFT(H106, FIND(":", H106)-1))</f>
@@ -6083,7 +6219,7 @@
         <v>1</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I107">
         <f>F107*VALUE(LEFT(H107, FIND(":", H107)-1))</f>
@@ -6112,7 +6248,7 @@
         <v>1</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I108">
         <f>F108*VALUE(LEFT(H108, FIND(":", H108)-1))</f>
@@ -6141,7 +6277,7 @@
         <v>1</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I109">
         <f>F109*VALUE(LEFT(H109, FIND(":", H109)-1))</f>
@@ -6170,7 +6306,7 @@
         <v>1</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I110">
         <f>F110*VALUE(LEFT(H110, FIND(":", H110)-1))</f>
@@ -6195,13 +6331,16 @@
         <v>285</v>
       </c>
       <c r="E111" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F111">
         <v>1</v>
       </c>
+      <c r="G111" s="1" t="s">
+        <v>360</v>
+      </c>
       <c r="H111" s="1" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="I111">
         <f>F111*VALUE(LEFT(H111, FIND(":", H111)-1))</f>
@@ -6230,10 +6369,10 @@
         <v>1</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I112">
         <f>F112*VALUE(LEFT(H112, FIND(":", H112)-1))</f>
@@ -6262,7 +6401,7 @@
         <v>1</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="I113">
         <f>F113*VALUE(LEFT(H113, FIND(":", H113)-1))</f>
@@ -6291,10 +6430,10 @@
         <v>1</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="I114">
         <f>F114*VALUE(LEFT(H114, FIND(":", H114)-1))</f>
@@ -6323,7 +6462,7 @@
         <v>1</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="I115">
         <f>F115*VALUE(LEFT(H115, FIND(":", H115)-1))</f>
@@ -6352,10 +6491,10 @@
         <v>1</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I116">
         <f>F116*VALUE(LEFT(H116, FIND(":", H116)-1))</f>
@@ -6386,10 +6525,10 @@
         <v>1</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I117">
         <f>F117*VALUE(LEFT(H117, FIND(":", H117)-1))</f>
@@ -6418,10 +6557,10 @@
         <v>1</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I118">
         <f>F118*VALUE(LEFT(H118, FIND(":", H118)-1))</f>
@@ -6450,10 +6589,10 @@
         <v>1</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I119">
         <f>F119*VALUE(LEFT(H119, FIND(":", H119)-1))</f>
@@ -6482,10 +6621,10 @@
         <v>1</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I120">
         <f>F120*VALUE(LEFT(H120, FIND(":", H120)-1))</f>
@@ -6514,10 +6653,10 @@
         <v>1</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I121">
         <f>F121*VALUE(LEFT(H121, FIND(":", H121)-1))</f>
@@ -6546,7 +6685,7 @@
         <v>1</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="I122">
         <f>F122*VALUE(LEFT(H122, FIND(":", H122)-1))</f>
@@ -6575,10 +6714,10 @@
         <v>1</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I123">
         <f>F123*VALUE(LEFT(H123, FIND(":", H123)-1))</f>
@@ -6609,10 +6748,10 @@
         <v>1</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I124">
         <f>F124*VALUE(LEFT(H124, FIND(":", H124)-1))</f>
@@ -6641,10 +6780,10 @@
         <v>1</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I125">
         <f>F125*VALUE(LEFT(H125, FIND(":", H125)-1))</f>
@@ -6673,10 +6812,10 @@
         <v>1</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I126">
         <f>F126*VALUE(LEFT(H126, FIND(":", H126)-1))</f>
@@ -6705,10 +6844,10 @@
         <v>1</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I127">
         <f>F127*VALUE(LEFT(H127, FIND(":", H127)-1))</f>
@@ -6737,10 +6876,10 @@
         <v>1</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I128">
         <f>F128*VALUE(LEFT(H128, FIND(":", H128)-1))</f>
@@ -6769,7 +6908,7 @@
         <v>1</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="I129">
         <f>F129*VALUE(LEFT(H129, FIND(":", H129)-1))</f>
@@ -6796,13 +6935,16 @@
         <v>304</v>
       </c>
       <c r="E130" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F130">
         <v>1</v>
       </c>
+      <c r="G130" s="1" t="s">
+        <v>375</v>
+      </c>
       <c r="H130" s="1" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="I130">
         <f>F130*VALUE(LEFT(H130, FIND(":", H130)-1))</f>
@@ -6825,13 +6967,16 @@
         <v>305</v>
       </c>
       <c r="E131" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F131">
         <v>1</v>
       </c>
+      <c r="G131" s="1" t="s">
+        <v>376</v>
+      </c>
       <c r="H131" s="1" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="I131">
         <f>F131*VALUE(LEFT(H131, FIND(":", H131)-1))</f>
@@ -6854,13 +6999,16 @@
         <v>306</v>
       </c>
       <c r="E132" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F132">
         <v>1</v>
       </c>
+      <c r="G132" s="1" t="s">
+        <v>377</v>
+      </c>
       <c r="H132" s="1" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="I132">
         <f>F132*VALUE(LEFT(H132, FIND(":", H132)-1))</f>
@@ -6889,7 +7037,7 @@
         <v>1</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="I133">
         <f>F133*VALUE(LEFT(H133, FIND(":", H133)-1))</f>
@@ -6912,13 +7060,16 @@
         <v>308</v>
       </c>
       <c r="E134" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F134">
         <v>1</v>
       </c>
+      <c r="G134" s="1" t="s">
+        <v>378</v>
+      </c>
       <c r="H134" s="1" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="I134">
         <f>F134*VALUE(LEFT(H134, FIND(":", H134)-1))</f>
@@ -7132,13 +7283,13 @@
       <formula1>"0: Not done,10: Policy in place and published"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H59">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: Low Maturity. Score Range (0-14),4: Developing. Score Range (15-30),7: Established. Score Range (31-42),10: Optimizing. Score Range (43-50)"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H60">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H61">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H62">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
@@ -7180,7 +7331,7 @@
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H75">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H76">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
@@ -7216,19 +7367,19 @@
       <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H87">
+      <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H88">
       <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H88">
-      <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H89">
       <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H90">
+      <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H91">
       <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H91">
-      <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H92">
       <formula1>"0: Not done,10: Completed"</formula1>
@@ -7288,7 +7439,7 @@
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H111">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H112">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
@@ -7345,19 +7496,19 @@
       <formula1>"0: None,10: communicates wins in KPI thresholds and unit costs"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H130">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H131">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: Low Maturity. Score Range (0-14),4: Developing. Score Range (15-30),7: Established. Score Range (31-42),10: Optimizing. Score Range (43-50)"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H132">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H133">
       <formula1>"0: Not monitored,2: Reported,5: Manual remediation,10: Automated remediation"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H134">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>

--- a/assessments/FinOps++/assessment.xlsx
+++ b/assessments/FinOps++/assessment.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1219" uniqueCount="455">
   <si>
     <t>Sum of Weights</t>
   </si>
@@ -952,13 +952,13 @@
     <t>1.0.0</t>
   </si>
   <si>
+    <t>2.0.0</t>
+  </si>
+  <si>
+    <t>2.1.0</t>
+  </si>
+  <si>
     <t>1.8.0</t>
-  </si>
-  <si>
-    <t>2.1.0</t>
-  </si>
-  <si>
-    <t>2.0.0</t>
   </si>
   <si>
     <t>1.6.1</t>
@@ -999,9 +999,119 @@
 * Periodically reevaluate the gap analysis and priority list based on lessons learned and new business goals.</t>
   </si>
   <si>
-    <t>* Define process for reviewing asking for credits from CSPs
-* Define frequency of review, etc.
-10*Ceil(x/2)</t>
+    <t>Measured over: the personas the practice depends on during the review period.
+* Personas listed (the personas the practice depends on are named, not assumed)
+* Need recorded per persona (what each one has to understand to play its part is written down)
+* Current level recorded (what each persona knows today is assessed against that need)
+* Gaps ranked (the gaps are ordered, so the next content produced has a stated reason)
+* Reassessed on a stated cadence (the assessment is repeated on a schedule with a named owner)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>Measured over: the personas the practice depends on during the review period.
+* Material exists per persona (each persona has content aimed at it rather than one general deck)
+* More than one level (content exists beyond an introduction, so somebody can go further)
+* Organization specific content included (material covers how FinOps works here, not only generic
+  concepts)
+* Onboarding carries it (new employees and contractors receive the material relevant to their
+  persona when they join)
+* Owner named (each curriculum records who maintains it)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>Measured over: the learning opportunities offered during the review period.
+* Certification route exists (a funded path to FinOps certification is offered, and who is eligible
+  is written down)
+* Informal sessions run on a stated cadence (office hours, lunch and learns or equivalent, on a
+  schedule rather than when somebody volunteers)
+* Opportunities counted (the number offered in the period is recorded)
+* Open beyond the practice (allied personas can attend, not only the FinOps team)
+10*Ceil(x/4)</t>
+  </si>
+  <si>
+    <t>Measured over: the vendor and provider training the practice points people to during the review
+period.
+* Catalogued per persona (the vendor training relevant to each persona is listed, with its cost and
+  the effort it takes)
+* Access arranged (people can reach the training without seeking approval each time, and who pays
+  is recorded)
+* Contextualized (each listed course carries a note on what applies here, including which services
+  the organization actually runs and which parts to skip)
+* Catalogue rechecked (the list is reviewed on a stated cadence, because vendors retire and replace
+  courses without telling anyone)
+10*Ceil(x/4)</t>
+  </si>
+  <si>
+    <t>Measured over: the personas the practice depends on, and the learning material published to them.
+* Completion measured (the share of each persona that finished the material intended for it)
+* Consultation measured (how often teams return to the material after the session that introduced
+  it)
+* Effect on a named measure reported (training is reported against a KPI it was meant to move, such
+  as tagging compliance or forecast accuracy)
+* Refresh path exists (material is reviewed on a stated cadence, and each review records what was
+  updated, retired, or kept)
+10*Ceil(x/4)</t>
+  </si>
+  <si>
+    <t>* Operating model recorded (which shape the team takes, whether a single central team, a fully virtual
+  team, or a hub and spoke with members embedded in Engineering, and where it reports)
+* Staffing plan recorded (the roles the practice needs, requested against filled, and which support is
+  virtual rather than hired)
+* Skills mapped (leadership, communication, analytical, and technical skills mapped to the roles, with
+  the gaps named)
+* Funding source named (the team has a standing budget line rather than a one-off allocation)
+* Decision model documented (how a cross-functional or urgent decision gets made, and who makes it)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>Measured over: the roadmap in force during the review period, and the items on its backlog.
+* Roadmap published (a roadmap for building the practice exists where the personas it affects can
+  read it)
+* Items carry an owner and a date (each backlog item names who is accountable and when it is due)
+* Prioritization stated (the rule used to order the backlog is written down, so two people ordering
+  it reach the same result)
+* Dependencies recorded (items blocked by another capability, a tool, or a hire say so)
+* Progress reviewed (completed and slipped items are reviewed on a stated cadence with a named owner)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>Measured over: the forecasting, budgeting, and procurement workflows the organization runs.
+* Forecasting consumes cost data (the forecast is built from the same cost data the practice
+  publishes, not a separate extract)
+* Budgeting consumes cost data (budget setting and tracking draw on it)
+* Procurement consumes cost data (renewal and purchase decisions see current and committed spend)
+* Delivered where the work happens (the data reaches each workflow in the tool its owners already
+  use rather than a FinOps report they must seek out)
+* Freshness stated (each workflow records how current the data it receives is)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>Measured over: the KPI set the practice publishes during the review period.
+* Published on a cadence (the KPI set is issued on a stated schedule rather than on request)
+* Reaches beyond the practice (the personas each KPI concerns receive it, not only the FinOps team)
+* Value of the practice included (at least one KPI reports the savings or cost avoidance the
+  practice generated)
+* Definitions travel with the numbers (each KPI states what it measures and over what period)
+* Movement explained (a change in a KPI is published with the reason, not only the new figure)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>Measured over: the personas the practice works with during the review period.
+* Named contacts (each persona the practice depends on has a named counterpart on both sides)
+* Regular contact (engagement happens on a stated cadence rather than when something breaks)
+* Wins published (savings and avoided cost are reported with the team that earned them named)
+* Misses published (targets that were missed are reported in the same place as the wins)
+* Requests tracked (a request to the practice carries an owner and a response, so a persona can see
+  what happened to it)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>Measured over: the tasks the practice performs more than once during the review period.
+* Repeated tasks inventoried (the tasks the practice repeats are listed, with how often each runs)
+* Effort recorded (each repeated task carries an estimate of the time it consumes)
+* Automation candidates ranked (tasks are ordered by effort saved against cost to automate)
+* Effect measured (time or cycle time before and after an automation is recorded)
+10*Ceil(x/4)</t>
   </si>
   <si>
     <t>* Weighted sum
@@ -1100,6 +1210,76 @@
 10*Ceil(x/3)</t>
   </si>
   <si>
+    <t>Measured over: every provider invoice received during the review period. Invoices arrive on a monthly
+cycle and are few enough to enumerate, so items are assessed against each one.
+* Intake defined (which provider invoices arrive, on what cycle, and who receives them)
+* Allocation mapping in place (invoice lines resolve to a cost center through the allocation model)
+* Ledger codes mapped (each cost type carries the general ledger code Finance posts it to)
+* Format and timing agreed (the output matches what accounting needs and arrives before close)
+* Unmapped lines reported (invoice lines that resolve to no cost center are reported in currency)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>Measured over: every provider invoice received during the review period.
+* Reconciliation cadence published (invoices are reconciled on a stated cadence with a named owner)
+* Scope stated (reconciliation covers rates, discounts, and credits rather than the total alone)
+* Completion measured against an SLA (the time from invoice receipt to reconciliation complete is
+  measured against a stated target)
+* Discrepancies recorded (each discrepancy carries its amount, its cause, and how it was resolved)
+* Finance reconciles independently (Finance completes a reconciliation without the central FinOps team
+  doing it for them)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>* Finance approval recorded (Finance is named in the chargeback rules and has signed off on them)
+* Allocation rules documented (which cost types reach which cost centers, including shared costs and
+  commitment discounts)
+* Showback and chargeback scope stated (which scopes are shown for information and which post to
+  official accounting budgets)
+* Cadence documented (when the run happens relative to financial close, and when cost centers receive
+  their figures)
+* Correction path documented (how a posted charge is corrected after close, including true-up entries)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>Scored at the highest stage the chargeback run reaches. A practice does not need the stages below it,
+because a run integrated into finance tooling has already replaced the spreadsheet it grew out of.</t>
+  </si>
+  <si>
+    <t>Measured over: every chargeback report issued during the review period, and every dispute raised
+against one.
+* Recipients named (each cost center has a named recipient for its report)
+* Distribution tied to close (reports reach recipients on a stated schedule relative to financial
+  close)
+* Cycle time measured (the time from close to report delivered is measured against a stated target)
+* Accuracy published with the report (recipients see the accuracy figure alongside their charges
+  rather than it being held internally)
+* Dispute outcomes recorded (each dispute records what was challenged, how it resolved, and whether
+  the charge changed)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>* Weighted sum
+  Chargeback accuracy (score x4),
+  Shared cost coverage (score x3),
+  Variance resolution (score x2),
+  Coverage reviewed (score x1).
+  Max raw (50)
+* Variance between what was charged and what was actually consumed, as a share of the amount charged
+  (0=Not measured, 1&gt;20%, 2=10-20%, 3=5-9%, 4=2-4%, 5 under 2%)
+* Share of shared cost allocated to the cost centers consuming it rather than held centrally
+  (0=Not measured, 1=None allocated, 2 under 25%, 3=25-49%, 4=50-79%, 5=80% or higher)
+* What happens to a variance once it is found
+  (0=Absorbed centrally without record, 1=Recorded, 2=Owner named,
+  3=Corrected by a true-up entry in the next close, 4=Root cause recorded against the correction,
+  5=Root cause feeds a change to the allocation rules)
+* How coverage is reviewed
+  (0=Not reviewed, 1=Discussed informally, 2=Reported for the period,
+  3=Reviewed with Finance on a stated cadence, 4=Candidate shared costs are listed with a reason for
+  each exclusion, 5=The exclusion list is worked down against a plan)
+* Output Range (0-50)</t>
+  </si>
+  <si>
     <t>* Document decision rights and approval authority for technology spend
 * Define and publish spend guardrails with named owners
 * Establish escalation path for spend exceptions
@@ -1116,6 +1296,22 @@
 * Deliver cost and outcome comparisons for competing initiatives at reviews
 * Track and report action follow-through from investment decisions
 10*Ceil(x/3)</t>
+  </si>
+  <si>
+    <t>Measured over: the review process itself for items 1 to 3, and every review conducted during the
+period for items 4 and 5. Reviews are few enough to enumerate, so those two are assessed against each
+review rather than as a coverage rate.
+* Intake trigger defined (which designs enter review: new builds, material changes, and spend above a
+  stated threshold)
+* Triage signals stated (candidates are prioritized using spend, usage, value, and adoption signals
+  rather than order of arrival)
+* Trade-off model documented (the review weighs cost, value, sovereignty, resilience, and
+  sustainability)
+* Approver named (the role that approves a placement decision and accepts its trade-offs is recorded
+  for each review)
+* Model updated from outcomes (the review records whether what was built matched what was approved,
+  and the trade-off model changes when it did not)
+10*Ceil(x/5)</t>
   </si>
   <si>
     <t>* Define process to address notifications from CSPs
@@ -1145,6 +1341,69 @@
 * Train teams on process
 * Automate process
 10*Ceil(x/3)</t>
+  </si>
+  <si>
+    <t>x = Resources and SaaS products requiring a license that are mapped to the specific entitlement
+covering them
+y = All resources and SaaS products identified as requiring a license
+x / y</t>
+  </si>
+  <si>
+    <t>Measured over: every license and SaaS agreement held during the review period.
+* Model recorded (each agreement records whether it is an organizational agreement, perpetual,
+  as-a-service, or a marketplace purchase)
+* Change terms recorded (whether licenses can be added mid-contract, and when they can be reduced)
+* Metered charges recorded (charges beyond the license itself, such as access counts, API calls, or
+  stored data)
+* Bring your own license eligibility tagged (resources running software under an existing license
+  carry a tag identifying them)
+* Allocation target named (each agreement records the cost center its cost reaches)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>Measured over: the license and SaaS billing and entitlement feeds in use during the review period.
+* Retrieved without a person (billing arrives on a schedule rather than being downloaded by hand)
+* Normalized schema (billing arrives in a common format such as FOCUS rather than per vendor
+  exports)
+* Entitlements joined (purchased quantities sit alongside the spend, so utilization can be computed)
+* Shared with asset management (contracts, usage and spend are available to the IT and software
+  asset management functions rather than held inside FinOps)
+* Named counterparts (Procurement, Finance and asset management each have a named contact)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>Measured over: every license and SaaS entitlement held during the review period.
+* Compliance checked (resources requiring a license are checked against the entitlements held, and
+  the shortfall or surplus is recorded)
+* Idle assignment identified (assigned licenses with no activity are identified against a stated
+  inactivity window)
+* Reclamation threshold stated (the usage level at which a license is reclaimed or reassigned is
+  written down)
+* Reclamation path exists (a license below the threshold can be reclaimed or reassigned through a
+  stated route, and each review records what was reclaimed, reassigned, or kept)
+* Triggers fire without a person (reclamation starts from the usage data rather than from somebody
+  remembering to look)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>Measured over: every workload design reviewed during the period that consumes licensed software.
+* License position supplied (the review receives what the organization already owns and what it
+  would need)
+* Options compared (the same workload is costed under infrastructure with an existing license,
+  a managed platform service, and a SaaS product)
+* Compliance checked (the design states whether the license terms permit the deployment)
+* Decision recorded (the option chosen and the licensing reason behind it are written into the
+  design record)
+10*Ceil(x/4)</t>
+  </si>
+  <si>
+    <t>Measured over: the license and SaaS reporting issued during the review period.
+* Published on a stated cadence (the report is issued on a schedule rather than on request)
+* Spend included (license and SaaS spend for the period, split by agreement)
+* Utilization included (assigned licenses divided by purchased licenses, as a rate)
+* Reaches the holders (the teams holding the licenses receive it, not only Procurement and Finance)
+* Renewal horizon shown (agreements approaching renewal are listed with their dates)
+10*Ceil(x/5)</t>
   </si>
   <si>
     <t>* Weighted sum
@@ -1532,81 +1791,78 @@
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 3, 'Condition': 'item 1 completed'}, {'Score': 5, 'Condition': 'items 1-2 completed'}, {'Score': 8, 'Condition': 'items 1-3 completed'}, {'Score': 10, 'Condition': 'items 1-4 completed'}]</t>
   </si>
   <si>
+    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': '1 item completed'}, {'Score': 4, 'Condition': '2 items completed'}, {'Score': 6, 'Condition': '3 items completed'}, {'Score': 8, 'Condition': '4 items completed'}, {'Score': 10, 'Condition': '5 items completed'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'Low Maturity (0-9)'}, {'Score': 4, 'Condition': 'Developing (10-18)'}, {'Score': 7, 'Condition': 'Established (19-26)'}, {'Score': 10, 'Condition': 'Optimizing (27-31)'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'Low Maturity, Score Range (0-8)'}, {'Score': 4, 'Condition': 'Developing, Score Range (9-17)'}, {'Score': 7, 'Condition': 'Established, Score Range (18-24)'}, {'Score': 10, 'Condition': 'Optimizing, Score Range (25-29)'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'Low Maturity, Score Range (0-15)'}, {'Score': 4, 'Condition': 'Developing, Score Range (16-31)'}, {'Score': 7, 'Condition': 'Established, Score Range (32-44)'}, {'Score': 10, 'Condition': 'Optimizing, Score Range (45-52)'}]</t>
+  </si>
+  <si>
     <t>[{'Score': 0, 'Condition': 'Not done'}, {'Score': 10, 'Condition': 'Completed'}]</t>
   </si>
   <si>
+    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': 'item 1 completed'}, {'Score': 4, 'Condition': 'items 1-2 completed'}, {'Score': 6, 'Condition': 'items 1-3 completed'}, {'Score': 8, 'Condition': 'items 1-4 completed'}, {'Score': 10, 'Condition': 'items 1-5 completed'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'Assembled in spreadsheets and posted by manual journal entry'}, {'Score': 2, 'Condition': 'Centralized tooling produces the figures, which are then exported and edited by hand'}, {'Score': 5, 'Condition': 'The run is automated end to end and a person posts the result'}, {'Score': 7, 'Condition': 'The run posts to the financial system, with a person reviewing before release'}, {'Score': 10, 'Condition': 'Chargeback and showback reporting is integrated automatically into finance tooling, with exceptions routed for review'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'Low Maturity, Score Range (0-14)'}, {'Score': 4, 'Condition': 'Developing, Score Range (15-30)'}, {'Score': 7, 'Condition': 'Established, Score Range (31-42)'}, {'Score': 10, 'Condition': 'Optimizing, Score Range (43-50)'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'No executive sponsor identified'}, {'Score': 10, 'Condition': 'Executive sponsor formally identified and actively engaged'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'No documented method'}, {'Score': 10, 'Condition': 'Documented method of assessing modernization efforts'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': '0%'}, {'Score': 1, 'Condition': '10%'}, {'Score': 2, 'Condition': '20%'}, {'Score': 3, 'Condition': '30%'}, {'Score': 4, 'Condition': '40%'}, {'Score': 5, 'Condition': '50%'}, {'Score': 6, 'Condition': '60%'}, {'Score': 7, 'Condition': '70%'}, {'Score': 8, 'Condition': '80%'}, {'Score': 9, 'Condition': '90%'}, {'Score': 10, 'Condition': 'Near 100%'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'Not done'}, {'Score': 10, 'Condition': 'Policy in place and published'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'No teardown/shutdown policy'}, {'Score': 3, 'Condition': 'Published policy'}, {'Score': 6, 'Condition': 'Classification tagged or otherwise identifiable'}, {'Score': 10, 'Condition': 'Enforced Policy with tagged/identifiable classifications'}]</t>
+  </si>
+  <si>
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 5, 'Condition': '1 item completed'}, {'Score': 10, 'Condition': '2 items completed'}]</t>
   </si>
   <si>
-    <t>[{'Score': 0, 'Condition': 'Not done'}, {'Score': 10, 'Condition': 'Defined'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'Low Maturity (0-9)'}, {'Score': 4, 'Condition': 'Developing (10-18)'}, {'Score': 7, 'Condition': 'Established (19-26)'}, {'Score': 10, 'Condition': 'Optimizing (27-31)'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'Low Maturity, Score Range (0-8)'}, {'Score': 4, 'Condition': 'Developing, Score Range (9-17)'}, {'Score': 7, 'Condition': 'Established, Score Range (18-24)'}, {'Score': 10, 'Condition': 'Optimizing, Score Range (25-29)'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'Low Maturity, Score Range (0-15)'}, {'Score': 4, 'Condition': 'Developing, Score Range (16-31)'}, {'Score': 7, 'Condition': 'Established, Score Range (32-44)'}, {'Score': 10, 'Condition': 'Optimizing, Score Range (45-52)'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': '1 item completed'}, {'Score': 4, 'Condition': '2 items completed'}, {'Score': 6, 'Condition': '3 items completed'}, {'Score': 8, 'Condition': '4 items completed'}, {'Score': 10, 'Condition': '5 items completed'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': 'item 1 completed'}, {'Score': 4, 'Condition': 'items 1-2 completed'}, {'Score': 6, 'Condition': 'items 1-3 completed'}, {'Score': 8, 'Condition': 'items 1-4 completed'}, {'Score': 10, 'Condition': 'items 1-5 completed'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'Not done'}, {'Score': 10, 'Condition': 'Done and clearly defined'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'No executive sponsor identified'}, {'Score': 10, 'Condition': 'Executive sponsor formally identified and actively engaged'}]</t>
+    <t>[{'Score': 0, 'Condition': '0%'}, {'Score': 1, 'Condition': '10%'}, {'Score': 2, 'Condition': '20%'}, {'Score': 3, 'Condition': '30%'}, {'Score': 4, 'Condition': '40%'}, {'Score': 5, 'Condition': '50%'}, {'Score': 6, 'Condition': '60%'}, {'Score': 7, 'Condition': '70%'}, {'Score': 8, 'Condition': '80% '}, {'Score': 9, 'Condition': '90%'}, {'Score': 10, 'Condition': 'Near 100%'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 5, 'Condition': '1 item  completed'}, {'Score': 10, 'Condition': '2 items completed'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': '1 item completed'}, {'Score': 4, 'Condition': '2 items completed'}, {'Score': 5, 'Condition': '3 items completed'}, {'Score': 7, 'Condition': '4 items completed'}, {'Score': 9, 'Condition': '5 items completed'}, {'Score': 10, 'Condition': '6 items completed'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'No alerting to any owners'}, {'Score': 1, 'Condition': 'Alerting in at least one owner'}, {'Score': 3, 'Condition': 'Alerting to some owners [&gt;20%]'}, {'Score': 6, 'Condition': 'Alerting to most owners [&gt;60%]'}, {'Score': 10, 'Condition': 'Alerting to all owners [100%]'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': '1 item completed'}, {'Score': 3, 'Condition': '2 items completed'}, {'Score': 4, 'Condition': '3 items completed'}, {'Score': 5, 'Condition': '4 items completed'}, {'Score': 7, 'Condition': '5 items completed'}, {'Score': 8, 'Condition': '6 items completed'}, {'Score': 9, 'Condition': '7 items completed'}, {'Score': 10, 'Condition': '8 items completed'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'Never'}, {'Score': 1, 'Condition': 'Monthly or greater'}, {'Score': 2, 'Condition': 'More than a week'}, {'Score': 3, 'Condition': '7 days'}, {'Score': 4, 'Condition': '5 days'}, {'Score': 6, 'Condition': '2 days'}, {'Score': 8, 'Condition': '1 day'}, {'Score': 10, 'Condition': 'Instant'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': '1 items completed'}, {'Score': 3, 'Condition': '2 items completed'}, {'Score': 5, 'Condition': '3 items completed'}, {'Score': 6, 'Condition': '4 items completed'}, {'Score': 8, 'Condition': '5 items completed'}, {'Score': 9, 'Condition': '6 items completed'}, {'Score': 10, 'Condition': '7 items completed'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'No alerting in workflow tools'}, {'Score': 1, 'Condition': 'Alerting in at least one tool'}, {'Score': 3, 'Condition': 'Alerting in some tooling [&gt;20%]'}, {'Score': 6, 'Condition': 'Alerting in most tooling [&gt;60%]'}, {'Score': 10, 'Condition': 'Alerting in all workflow tools [100%]'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'No review of trends'}, {'Score': 3, 'Condition': 'Manual review of trends'}, {'Score': 6, 'Condition': 'Automated trend detection'}, {'Score': 10, 'Condition': 'Manual review and automated trend detection'}]</t>
   </si>
   <si>
     <t>[{'Score': 0, 'Condition': 'Does not exist'}, {'Score': 10, 'Condition': 'Exists'}]</t>
   </si>
   <si>
-    <t>[{'Score': 0, 'Condition': 'No documented method'}, {'Score': 10, 'Condition': 'Documented method of assessing modernization efforts'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': '0%'}, {'Score': 1, 'Condition': '10%'}, {'Score': 2, 'Condition': '20%'}, {'Score': 3, 'Condition': '30%'}, {'Score': 4, 'Condition': '40%'}, {'Score': 5, 'Condition': '50%'}, {'Score': 6, 'Condition': '60%'}, {'Score': 7, 'Condition': '70%'}, {'Score': 8, 'Condition': '80%'}, {'Score': 9, 'Condition': '90%'}, {'Score': 10, 'Condition': 'Near 100%'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'Not done'}, {'Score': 10, 'Condition': 'Policy in place and published'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'Low Maturity, Score Range (0-14)'}, {'Score': 4, 'Condition': 'Developing, Score Range (15-30)'}, {'Score': 7, 'Condition': 'Established, Score Range (31-42)'}, {'Score': 10, 'Condition': 'Optimizing, Score Range (43-50)'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'No teardown/shutdown policy'}, {'Score': 3, 'Condition': 'Published policy'}, {'Score': 6, 'Condition': 'Classification tagged or otherwise identifiable'}, {'Score': 10, 'Condition': 'Enforced Policy with tagged/identifiable classifications'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': '0%'}, {'Score': 1, 'Condition': '10%'}, {'Score': 2, 'Condition': '20%'}, {'Score': 3, 'Condition': '30%'}, {'Score': 4, 'Condition': '40%'}, {'Score': 5, 'Condition': '50%'}, {'Score': 6, 'Condition': '60%'}, {'Score': 7, 'Condition': '70%'}, {'Score': 8, 'Condition': '80% '}, {'Score': 9, 'Condition': '90%'}, {'Score': 10, 'Condition': 'Near 100%'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 5, 'Condition': '1 item  completed'}, {'Score': 10, 'Condition': '2 items completed'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': '1 item completed'}, {'Score': 4, 'Condition': '2 items completed'}, {'Score': 5, 'Condition': '3 items completed'}, {'Score': 7, 'Condition': '4 items completed'}, {'Score': 9, 'Condition': '5 items completed'}, {'Score': 10, 'Condition': '6 items completed'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'No alerting to any owners'}, {'Score': 1, 'Condition': 'Alerting in at least one owner'}, {'Score': 3, 'Condition': 'Alerting to some owners [&gt;20%]'}, {'Score': 6, 'Condition': 'Alerting to most owners [&gt;60%]'}, {'Score': 10, 'Condition': 'Alerting to all owners [100%]'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': '1 item completed'}, {'Score': 3, 'Condition': '2 items completed'}, {'Score': 4, 'Condition': '3 items completed'}, {'Score': 5, 'Condition': '4 items completed'}, {'Score': 7, 'Condition': '5 items completed'}, {'Score': 8, 'Condition': '6 items completed'}, {'Score': 9, 'Condition': '7 items completed'}, {'Score': 10, 'Condition': '8 items completed'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'Never'}, {'Score': 1, 'Condition': 'Monthly or greater'}, {'Score': 2, 'Condition': 'More than a week'}, {'Score': 3, 'Condition': '7 days'}, {'Score': 4, 'Condition': '5 days'}, {'Score': 6, 'Condition': '2 days'}, {'Score': 8, 'Condition': '1 day'}, {'Score': 10, 'Condition': 'Instant'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': '1 items completed'}, {'Score': 3, 'Condition': '2 items completed'}, {'Score': 5, 'Condition': '3 items completed'}, {'Score': 6, 'Condition': '4 items completed'}, {'Score': 8, 'Condition': '5 items completed'}, {'Score': 9, 'Condition': '6 items completed'}, {'Score': 10, 'Condition': '7 items completed'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'No alerting in workflow tools'}, {'Score': 1, 'Condition': 'Alerting in at least one tool'}, {'Score': 3, 'Condition': 'Alerting in some tooling [&gt;20%]'}, {'Score': 6, 'Condition': 'Alerting in most tooling [&gt;60%]'}, {'Score': 10, 'Condition': 'Alerting in all workflow tools [100%]'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'No review of trends'}, {'Score': 3, 'Condition': 'Manual review of trends'}, {'Score': 6, 'Condition': 'Automated trend detection'}, {'Score': 10, 'Condition': 'Manual review and automated trend detection'}]</t>
-  </si>
-  <si>
     <t>[{'Score': 0, 'Condition': 'None'}, {'Score': 1, 'Condition': 'Annual'}, {'Score': 2, 'Condition': 'Quarterly'}, {'Score': 5, 'Condition': 'Monthly'}, {'Score': 7, 'Condition': 'Bi-Weekly'}, {'Score': 8, 'Condition': 'Weekly'}, {'Score': 10, 'Condition': 'Daily'}]</t>
   </si>
   <si>
@@ -1628,46 +1884,49 @@
     <t>0: No items completed</t>
   </si>
   <si>
+    <t>0: Low Maturity (0-9)</t>
+  </si>
+  <si>
+    <t>0: Low Maturity. Score Range (0-8)</t>
+  </si>
+  <si>
+    <t>0: Low Maturity. Score Range (0-15)</t>
+  </si>
+  <si>
     <t>0: Not done</t>
   </si>
   <si>
-    <t>0: Low Maturity (0-9)</t>
-  </si>
-  <si>
-    <t>0: Low Maturity. Score Range (0-8)</t>
-  </si>
-  <si>
-    <t>0: Low Maturity. Score Range (0-15)</t>
+    <t>0: Assembled in spreadsheets and posted by manual journal entry</t>
+  </si>
+  <si>
+    <t>0: Low Maturity. Score Range (0-14)</t>
   </si>
   <si>
     <t>0: No executive sponsor identified</t>
   </si>
   <si>
+    <t>0: No documented method</t>
+  </si>
+  <si>
+    <t>0: 0%</t>
+  </si>
+  <si>
+    <t>0: No teardown/shutdown policy</t>
+  </si>
+  <si>
+    <t>0: No alerting to any owners</t>
+  </si>
+  <si>
+    <t>0: Never</t>
+  </si>
+  <si>
+    <t>0: No alerting in workflow tools</t>
+  </si>
+  <si>
+    <t>0: No review of trends</t>
+  </si>
+  <si>
     <t>0: Does not exist</t>
-  </si>
-  <si>
-    <t>0: No documented method</t>
-  </si>
-  <si>
-    <t>0: 0%</t>
-  </si>
-  <si>
-    <t>0: Low Maturity. Score Range (0-14)</t>
-  </si>
-  <si>
-    <t>0: No teardown/shutdown policy</t>
-  </si>
-  <si>
-    <t>0: No alerting to any owners</t>
-  </si>
-  <si>
-    <t>0: Never</t>
-  </si>
-  <si>
-    <t>0: No alerting in workflow tools</t>
-  </si>
-  <si>
-    <t>0: No review of trends</t>
   </si>
   <si>
     <t>0: None</t>
@@ -3009,7 +3268,7 @@
         <v>316</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>413</v>
+        <v>435</v>
       </c>
       <c r="I2">
         <f>F2*VALUE(LEFT(H2, FIND(":", H2)-1))</f>
@@ -3041,7 +3300,7 @@
         <v>317</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I3">
         <f>F3*VALUE(LEFT(H3, FIND(":", H3)-1))</f>
@@ -3073,7 +3332,7 @@
         <v>318</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I4">
         <f>F4*VALUE(LEFT(H4, FIND(":", H4)-1))</f>
@@ -3105,7 +3364,7 @@
         <v>319</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I5">
         <f>F5*VALUE(LEFT(H5, FIND(":", H5)-1))</f>
@@ -3137,7 +3396,7 @@
         <v>320</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I6">
         <f>F6*VALUE(LEFT(H6, FIND(":", H6)-1))</f>
@@ -3162,13 +3421,16 @@
         <v>181</v>
       </c>
       <c r="E7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
+      <c r="G7" s="1" t="s">
+        <v>321</v>
+      </c>
       <c r="H7" s="1" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="I7">
         <f>F7*VALUE(LEFT(H7, FIND(":", H7)-1))</f>
@@ -3191,13 +3453,16 @@
         <v>182</v>
       </c>
       <c r="E8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
+      <c r="G8" s="1" t="s">
+        <v>322</v>
+      </c>
       <c r="H8" s="1" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="I8">
         <f>F8*VALUE(LEFT(H8, FIND(":", H8)-1))</f>
@@ -3220,13 +3485,16 @@
         <v>183</v>
       </c>
       <c r="E9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
+      <c r="G9" s="1" t="s">
+        <v>323</v>
+      </c>
       <c r="H9" s="1" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="I9">
         <f>F9*VALUE(LEFT(H9, FIND(":", H9)-1))</f>
@@ -3255,10 +3523,10 @@
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I10">
         <f>F10*VALUE(LEFT(H10, FIND(":", H10)-1))</f>
@@ -3281,13 +3549,16 @@
         <v>185</v>
       </c>
       <c r="E11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
+      <c r="G11" s="1" t="s">
+        <v>325</v>
+      </c>
       <c r="H11" s="1" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="I11">
         <f>F11*VALUE(LEFT(H11, FIND(":", H11)-1))</f>
@@ -3317,8 +3588,11 @@
       <c r="F12">
         <v>1</v>
       </c>
+      <c r="G12" s="1" t="s">
+        <v>326</v>
+      </c>
       <c r="H12" s="1" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="I12">
         <f>F12*VALUE(LEFT(H12, FIND(":", H12)-1))</f>
@@ -3341,13 +3615,16 @@
         <v>187</v>
       </c>
       <c r="E13" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
+      <c r="G13" s="1" t="s">
+        <v>327</v>
+      </c>
       <c r="H13" s="1" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="I13">
         <f>F13*VALUE(LEFT(H13, FIND(":", H13)-1))</f>
@@ -3370,13 +3647,16 @@
         <v>188</v>
       </c>
       <c r="E14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
+      <c r="G14" s="1" t="s">
+        <v>328</v>
+      </c>
       <c r="H14" s="1" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="I14">
         <f>F14*VALUE(LEFT(H14, FIND(":", H14)-1))</f>
@@ -3399,13 +3679,16 @@
         <v>189</v>
       </c>
       <c r="E15" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
+      <c r="G15" s="1" t="s">
+        <v>329</v>
+      </c>
       <c r="H15" s="1" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="I15">
         <f>F15*VALUE(LEFT(H15, FIND(":", H15)-1))</f>
@@ -3428,13 +3711,16 @@
         <v>190</v>
       </c>
       <c r="E16" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
+      <c r="G16" s="1" t="s">
+        <v>330</v>
+      </c>
       <c r="H16" s="1" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="I16">
         <f>F16*VALUE(LEFT(H16, FIND(":", H16)-1))</f>
@@ -3457,13 +3743,16 @@
         <v>191</v>
       </c>
       <c r="E17" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
+      <c r="G17" s="1" t="s">
+        <v>331</v>
+      </c>
       <c r="H17" s="1" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="I17">
         <f>F17*VALUE(LEFT(H17, FIND(":", H17)-1))</f>
@@ -3494,10 +3783,10 @@
         <v>1</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>416</v>
+        <v>437</v>
       </c>
       <c r="I18">
         <f>F18*VALUE(LEFT(H18, FIND(":", H18)-1))</f>
@@ -3526,10 +3815,10 @@
         <v>1</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="I19">
         <f>F19*VALUE(LEFT(H19, FIND(":", H19)-1))</f>
@@ -3558,10 +3847,10 @@
         <v>1</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>418</v>
+        <v>439</v>
       </c>
       <c r="I20">
         <f>F20*VALUE(LEFT(H20, FIND(":", H20)-1))</f>
@@ -3584,16 +3873,16 @@
         <v>195</v>
       </c>
       <c r="E21" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I21">
         <f>F21*VALUE(LEFT(H21, FIND(":", H21)-1))</f>
@@ -3622,7 +3911,7 @@
         <v>1</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="I22">
         <f>F22*VALUE(LEFT(H22, FIND(":", H22)-1))</f>
@@ -3653,10 +3942,10 @@
         <v>1</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I23">
         <f>F23*VALUE(LEFT(H23, FIND(":", H23)-1))</f>
@@ -3685,10 +3974,10 @@
         <v>1</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I24">
         <f>F24*VALUE(LEFT(H24, FIND(":", H24)-1))</f>
@@ -3717,10 +4006,10 @@
         <v>1</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I25">
         <f>F25*VALUE(LEFT(H25, FIND(":", H25)-1))</f>
@@ -3749,10 +4038,10 @@
         <v>1</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I26">
         <f>F26*VALUE(LEFT(H26, FIND(":", H26)-1))</f>
@@ -3781,10 +4070,10 @@
         <v>1</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I27">
         <f>F27*VALUE(LEFT(H27, FIND(":", H27)-1))</f>
@@ -3813,10 +4102,10 @@
         <v>1</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I28">
         <f>F28*VALUE(LEFT(H28, FIND(":", H28)-1))</f>
@@ -3841,13 +4130,16 @@
         <v>203</v>
       </c>
       <c r="E29" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
+      <c r="G29" s="1" t="s">
+        <v>342</v>
+      </c>
       <c r="H29" s="1" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="I29">
         <f>F29*VALUE(LEFT(H29, FIND(":", H29)-1))</f>
@@ -3870,13 +4162,16 @@
         <v>204</v>
       </c>
       <c r="E30" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F30">
         <v>1</v>
       </c>
+      <c r="G30" s="1" t="s">
+        <v>343</v>
+      </c>
       <c r="H30" s="1" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="I30">
         <f>F30*VALUE(LEFT(H30, FIND(":", H30)-1))</f>
@@ -3904,8 +4199,11 @@
       <c r="F31">
         <v>1</v>
       </c>
+      <c r="G31" s="1" t="s">
+        <v>344</v>
+      </c>
       <c r="H31" s="1" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="I31">
         <f>F31*VALUE(LEFT(H31, FIND(":", H31)-1))</f>
@@ -3928,13 +4226,16 @@
         <v>206</v>
       </c>
       <c r="E32" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
+      <c r="G32" s="1" t="s">
+        <v>345</v>
+      </c>
       <c r="H32" s="1" t="s">
-        <v>415</v>
+        <v>441</v>
       </c>
       <c r="I32">
         <f>F32*VALUE(LEFT(H32, FIND(":", H32)-1))</f>
@@ -3957,13 +4258,16 @@
         <v>207</v>
       </c>
       <c r="E33" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F33">
         <v>1</v>
       </c>
+      <c r="G33" s="1" t="s">
+        <v>346</v>
+      </c>
       <c r="H33" s="1" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="I33">
         <f>F33*VALUE(LEFT(H33, FIND(":", H33)-1))</f>
@@ -3991,8 +4295,11 @@
       <c r="F34">
         <v>1</v>
       </c>
+      <c r="G34" s="1" t="s">
+        <v>347</v>
+      </c>
       <c r="H34" s="1" t="s">
-        <v>415</v>
+        <v>442</v>
       </c>
       <c r="I34">
         <f>F34*VALUE(LEFT(H34, FIND(":", H34)-1))</f>
@@ -4023,7 +4330,7 @@
         <v>1</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>419</v>
+        <v>443</v>
       </c>
       <c r="I35">
         <f>F35*VALUE(LEFT(H35, FIND(":", H35)-1))</f>
@@ -4052,10 +4359,10 @@
         <v>1</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>332</v>
+        <v>348</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I36">
         <f>F36*VALUE(LEFT(H36, FIND(":", H36)-1))</f>
@@ -4084,10 +4391,10 @@
         <v>1</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I37">
         <f>F37*VALUE(LEFT(H37, FIND(":", H37)-1))</f>
@@ -4116,10 +4423,10 @@
         <v>1</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I38">
         <f>F38*VALUE(LEFT(H38, FIND(":", H38)-1))</f>
@@ -4151,8 +4458,11 @@
       <c r="F39">
         <v>1</v>
       </c>
+      <c r="G39" s="1" t="s">
+        <v>351</v>
+      </c>
       <c r="H39" s="1" t="s">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c r="I39">
         <f>F39*VALUE(LEFT(H39, FIND(":", H39)-1))</f>
@@ -4175,16 +4485,16 @@
         <v>214</v>
       </c>
       <c r="E40" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F40">
         <v>1</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>335</v>
+        <v>352</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I40">
         <f>F40*VALUE(LEFT(H40, FIND(":", H40)-1))</f>
@@ -4207,13 +4517,13 @@
         <v>215</v>
       </c>
       <c r="E41" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F41">
         <v>1</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>421</v>
+        <v>444</v>
       </c>
       <c r="I41">
         <f>F41*VALUE(LEFT(H41, FIND(":", H41)-1))</f>
@@ -4236,16 +4546,16 @@
         <v>216</v>
       </c>
       <c r="E42" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F42">
         <v>1</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I42">
         <f>F42*VALUE(LEFT(H42, FIND(":", H42)-1))</f>
@@ -4268,16 +4578,16 @@
         <v>217</v>
       </c>
       <c r="E43" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F43">
         <v>1</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>337</v>
+        <v>354</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I43">
         <f>F43*VALUE(LEFT(H43, FIND(":", H43)-1))</f>
@@ -4306,7 +4616,7 @@
         <v>1</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="I44">
         <f>F44*VALUE(LEFT(H44, FIND(":", H44)-1))</f>
@@ -4335,7 +4645,7 @@
         <v>1</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="I45">
         <f>F45*VALUE(LEFT(H45, FIND(":", H45)-1))</f>
@@ -4364,7 +4674,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="I46">
         <f>F46*VALUE(LEFT(H46, FIND(":", H46)-1))</f>
@@ -4387,16 +4697,16 @@
         <v>221</v>
       </c>
       <c r="E47" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F47">
         <v>1</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I47">
         <f>F47*VALUE(LEFT(H47, FIND(":", H47)-1))</f>
@@ -4425,7 +4735,7 @@
         <v>1</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="I48">
         <f>F48*VALUE(LEFT(H48, FIND(":", H48)-1))</f>
@@ -4454,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="I49">
         <f>F49*VALUE(LEFT(H49, FIND(":", H49)-1))</f>
@@ -4483,7 +4793,7 @@
         <v>1</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="I50">
         <f>F50*VALUE(LEFT(H50, FIND(":", H50)-1))</f>
@@ -4513,8 +4823,11 @@
       <c r="F51">
         <v>1</v>
       </c>
+      <c r="G51" s="1" t="s">
+        <v>356</v>
+      </c>
       <c r="H51" s="1" t="s">
-        <v>422</v>
+        <v>445</v>
       </c>
       <c r="I51">
         <f>F51*VALUE(LEFT(H51, FIND(":", H51)-1))</f>
@@ -4537,13 +4850,16 @@
         <v>226</v>
       </c>
       <c r="E52" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F52">
         <v>1</v>
       </c>
+      <c r="G52" s="1" t="s">
+        <v>357</v>
+      </c>
       <c r="H52" s="1" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="I52">
         <f>F52*VALUE(LEFT(H52, FIND(":", H52)-1))</f>
@@ -4566,13 +4882,16 @@
         <v>227</v>
       </c>
       <c r="E53" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
+      <c r="G53" s="1" t="s">
+        <v>358</v>
+      </c>
       <c r="H53" s="1" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="I53">
         <f>F53*VALUE(LEFT(H53, FIND(":", H53)-1))</f>
@@ -4600,8 +4919,11 @@
       <c r="F54">
         <v>1</v>
       </c>
+      <c r="G54" s="1" t="s">
+        <v>359</v>
+      </c>
       <c r="H54" s="1" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="I54">
         <f>F54*VALUE(LEFT(H54, FIND(":", H54)-1))</f>
@@ -4624,13 +4946,16 @@
         <v>229</v>
       </c>
       <c r="E55" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F55">
         <v>1</v>
       </c>
+      <c r="G55" s="1" t="s">
+        <v>360</v>
+      </c>
       <c r="H55" s="1" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="I55">
         <f>F55*VALUE(LEFT(H55, FIND(":", H55)-1))</f>
@@ -4653,13 +4978,16 @@
         <v>230</v>
       </c>
       <c r="E56" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F56">
         <v>1</v>
       </c>
+      <c r="G56" s="1" t="s">
+        <v>361</v>
+      </c>
       <c r="H56" s="1" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="I56">
         <f>F56*VALUE(LEFT(H56, FIND(":", H56)-1))</f>
@@ -4684,13 +5012,13 @@
         <v>231</v>
       </c>
       <c r="E57" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F57">
         <v>1</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="I57">
         <f>F57*VALUE(LEFT(H57, FIND(":", H57)-1))</f>
@@ -4713,13 +5041,13 @@
         <v>232</v>
       </c>
       <c r="E58" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F58">
         <v>1</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="I58">
         <f>F58*VALUE(LEFT(H58, FIND(":", H58)-1))</f>
@@ -4742,16 +5070,16 @@
         <v>233</v>
       </c>
       <c r="E59" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>339</v>
+        <v>362</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>423</v>
+        <v>442</v>
       </c>
       <c r="I59">
         <f>F59*VALUE(LEFT(H59, FIND(":", H59)-1))</f>
@@ -4774,16 +5102,16 @@
         <v>234</v>
       </c>
       <c r="E60" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F60">
         <v>1</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>340</v>
+        <v>363</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I60">
         <f>F60*VALUE(LEFT(H60, FIND(":", H60)-1))</f>
@@ -4806,16 +5134,16 @@
         <v>235</v>
       </c>
       <c r="E61" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>341</v>
+        <v>364</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I61">
         <f>F61*VALUE(LEFT(H61, FIND(":", H61)-1))</f>
@@ -4838,16 +5166,16 @@
         <v>236</v>
       </c>
       <c r="E62" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F62">
         <v>1</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>342</v>
+        <v>365</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I62">
         <f>F62*VALUE(LEFT(H62, FIND(":", H62)-1))</f>
@@ -4878,7 +5206,7 @@
         <v>1</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="I63">
         <f>F63*VALUE(LEFT(H63, FIND(":", H63)-1))</f>
@@ -4901,13 +5229,13 @@
         <v>238</v>
       </c>
       <c r="E64" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F64">
         <v>1</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>424</v>
+        <v>446</v>
       </c>
       <c r="I64">
         <f>F64*VALUE(LEFT(H64, FIND(":", H64)-1))</f>
@@ -4930,13 +5258,13 @@
         <v>239</v>
       </c>
       <c r="E65" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F65">
         <v>1</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>422</v>
+        <v>445</v>
       </c>
       <c r="I65">
         <f>F65*VALUE(LEFT(H65, FIND(":", H65)-1))</f>
@@ -4965,7 +5293,7 @@
         <v>1</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="I66">
         <f>F66*VALUE(LEFT(H66, FIND(":", H66)-1))</f>
@@ -4994,7 +5322,7 @@
         <v>1</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="I67">
         <f>F67*VALUE(LEFT(H67, FIND(":", H67)-1))</f>
@@ -5023,7 +5351,7 @@
         <v>1</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="I68">
         <f>F68*VALUE(LEFT(H68, FIND(":", H68)-1))</f>
@@ -5048,16 +5376,16 @@
         <v>243</v>
       </c>
       <c r="E69" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I69">
         <f>F69*VALUE(LEFT(H69, FIND(":", H69)-1))</f>
@@ -5080,16 +5408,16 @@
         <v>244</v>
       </c>
       <c r="E70" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F70">
         <v>1</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>344</v>
+        <v>367</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>422</v>
+        <v>445</v>
       </c>
       <c r="I70">
         <f>F70*VALUE(LEFT(H70, FIND(":", H70)-1))</f>
@@ -5112,16 +5440,16 @@
         <v>245</v>
       </c>
       <c r="E71" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F71">
         <v>1</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I71">
         <f>F71*VALUE(LEFT(H71, FIND(":", H71)-1))</f>
@@ -5144,16 +5472,16 @@
         <v>246</v>
       </c>
       <c r="E72" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F72">
         <v>1</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>346</v>
+        <v>369</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>422</v>
+        <v>445</v>
       </c>
       <c r="I72">
         <f>F72*VALUE(LEFT(H72, FIND(":", H72)-1))</f>
@@ -5176,16 +5504,16 @@
         <v>247</v>
       </c>
       <c r="E73" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F73">
         <v>1</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>347</v>
+        <v>370</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>422</v>
+        <v>445</v>
       </c>
       <c r="I73">
         <f>F73*VALUE(LEFT(H73, FIND(":", H73)-1))</f>
@@ -5208,16 +5536,16 @@
         <v>248</v>
       </c>
       <c r="E74" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F74">
         <v>1</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>348</v>
+        <v>371</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I74">
         <f>F74*VALUE(LEFT(H74, FIND(":", H74)-1))</f>
@@ -5240,16 +5568,16 @@
         <v>249</v>
       </c>
       <c r="E75" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F75">
         <v>1</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>349</v>
+        <v>372</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I75">
         <f>F75*VALUE(LEFT(H75, FIND(":", H75)-1))</f>
@@ -5274,16 +5602,16 @@
         <v>250</v>
       </c>
       <c r="E76" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F76">
         <v>1</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I76">
         <f>F76*VALUE(LEFT(H76, FIND(":", H76)-1))</f>
@@ -5306,16 +5634,16 @@
         <v>251</v>
       </c>
       <c r="E77" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F77">
         <v>1</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I77">
         <f>F77*VALUE(LEFT(H77, FIND(":", H77)-1))</f>
@@ -5338,13 +5666,13 @@
         <v>252</v>
       </c>
       <c r="E78" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F78">
         <v>1</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>425</v>
+        <v>447</v>
       </c>
       <c r="I78">
         <f>F78*VALUE(LEFT(H78, FIND(":", H78)-1))</f>
@@ -5373,10 +5701,10 @@
         <v>1</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>352</v>
+        <v>375</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I79">
         <f>F79*VALUE(LEFT(H79, FIND(":", H79)-1))</f>
@@ -5405,10 +5733,10 @@
         <v>1</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>353</v>
+        <v>376</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I80">
         <f>F80*VALUE(LEFT(H80, FIND(":", H80)-1))</f>
@@ -5431,16 +5759,16 @@
         <v>255</v>
       </c>
       <c r="E81" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F81">
         <v>1</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>354</v>
+        <v>377</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I81">
         <f>F81*VALUE(LEFT(H81, FIND(":", H81)-1))</f>
@@ -5469,10 +5797,10 @@
         <v>1</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>423</v>
+        <v>442</v>
       </c>
       <c r="I82">
         <f>F82*VALUE(LEFT(H82, FIND(":", H82)-1))</f>
@@ -5503,7 +5831,7 @@
         <v>1</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="I83">
         <f>F83*VALUE(LEFT(H83, FIND(":", H83)-1))</f>
@@ -5532,7 +5860,7 @@
         <v>1</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="I84">
         <f>F84*VALUE(LEFT(H84, FIND(":", H84)-1))</f>
@@ -5561,7 +5889,7 @@
         <v>1</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="I85">
         <f>F85*VALUE(LEFT(H85, FIND(":", H85)-1))</f>
@@ -5584,13 +5912,13 @@
         <v>260</v>
       </c>
       <c r="E86" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F86">
         <v>1</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>426</v>
+        <v>448</v>
       </c>
       <c r="I86">
         <f>F86*VALUE(LEFT(H86, FIND(":", H86)-1))</f>
@@ -5619,7 +5947,7 @@
         <v>1</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>426</v>
+        <v>448</v>
       </c>
       <c r="I87">
         <f>F87*VALUE(LEFT(H87, FIND(":", H87)-1))</f>
@@ -5648,7 +5976,7 @@
         <v>1</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="I88">
         <f>F88*VALUE(LEFT(H88, FIND(":", H88)-1))</f>
@@ -5671,16 +5999,16 @@
         <v>263</v>
       </c>
       <c r="E89" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F89">
         <v>1</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>356</v>
+        <v>379</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I89">
         <f>F89*VALUE(LEFT(H89, FIND(":", H89)-1))</f>
@@ -5703,16 +6031,16 @@
         <v>264</v>
       </c>
       <c r="E90" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F90">
         <v>1</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>357</v>
+        <v>380</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I90">
         <f>F90*VALUE(LEFT(H90, FIND(":", H90)-1))</f>
@@ -5741,7 +6069,7 @@
         <v>1</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="I91">
         <f>F91*VALUE(LEFT(H91, FIND(":", H91)-1))</f>
@@ -5772,7 +6100,7 @@
         <v>1</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="I92">
         <f>F92*VALUE(LEFT(H92, FIND(":", H92)-1))</f>
@@ -5795,16 +6123,16 @@
         <v>267</v>
       </c>
       <c r="E93" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F93">
         <v>1</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>358</v>
+        <v>381</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I93">
         <f>F93*VALUE(LEFT(H93, FIND(":", H93)-1))</f>
@@ -5827,16 +6155,16 @@
         <v>268</v>
       </c>
       <c r="E94" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F94">
         <v>1</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>359</v>
+        <v>382</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I94">
         <f>F94*VALUE(LEFT(H94, FIND(":", H94)-1))</f>
@@ -5865,7 +6193,7 @@
         <v>1</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="I95">
         <f>F95*VALUE(LEFT(H95, FIND(":", H95)-1))</f>
@@ -5888,13 +6216,13 @@
         <v>270</v>
       </c>
       <c r="E96" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F96">
         <v>1</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>427</v>
+        <v>449</v>
       </c>
       <c r="I96">
         <f>F96*VALUE(LEFT(H96, FIND(":", H96)-1))</f>
@@ -5923,7 +6251,7 @@
         <v>1</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="I97">
         <f>F97*VALUE(LEFT(H97, FIND(":", H97)-1))</f>
@@ -5952,7 +6280,7 @@
         <v>1</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="I98">
         <f>F98*VALUE(LEFT(H98, FIND(":", H98)-1))</f>
@@ -5985,7 +6313,7 @@
         <v>1</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="I99">
         <f>F99*VALUE(LEFT(H99, FIND(":", H99)-1))</f>
@@ -6014,7 +6342,7 @@
         <v>1</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="I100">
         <f>F100*VALUE(LEFT(H100, FIND(":", H100)-1))</f>
@@ -6043,7 +6371,7 @@
         <v>1</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="I101">
         <f>F101*VALUE(LEFT(H101, FIND(":", H101)-1))</f>
@@ -6072,7 +6400,7 @@
         <v>1</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="I102">
         <f>F102*VALUE(LEFT(H102, FIND(":", H102)-1))</f>
@@ -6095,13 +6423,13 @@
         <v>277</v>
       </c>
       <c r="E103" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F103">
         <v>1</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>428</v>
+        <v>450</v>
       </c>
       <c r="I103">
         <f>F103*VALUE(LEFT(H103, FIND(":", H103)-1))</f>
@@ -6130,7 +6458,7 @@
         <v>1</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="I104">
         <f>F104*VALUE(LEFT(H104, FIND(":", H104)-1))</f>
@@ -6155,13 +6483,13 @@
         <v>279</v>
       </c>
       <c r="E105" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F105">
         <v>1</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>420</v>
+        <v>451</v>
       </c>
       <c r="I105">
         <f>F105*VALUE(LEFT(H105, FIND(":", H105)-1))</f>
@@ -6184,13 +6512,13 @@
         <v>280</v>
       </c>
       <c r="E106" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F106">
         <v>1</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>420</v>
+        <v>451</v>
       </c>
       <c r="I106">
         <f>F106*VALUE(LEFT(H106, FIND(":", H106)-1))</f>
@@ -6219,7 +6547,7 @@
         <v>1</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="I107">
         <f>F107*VALUE(LEFT(H107, FIND(":", H107)-1))</f>
@@ -6248,7 +6576,7 @@
         <v>1</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="I108">
         <f>F108*VALUE(LEFT(H108, FIND(":", H108)-1))</f>
@@ -6277,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="I109">
         <f>F109*VALUE(LEFT(H109, FIND(":", H109)-1))</f>
@@ -6306,7 +6634,7 @@
         <v>1</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="I110">
         <f>F110*VALUE(LEFT(H110, FIND(":", H110)-1))</f>
@@ -6331,16 +6659,16 @@
         <v>285</v>
       </c>
       <c r="E111" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F111">
         <v>1</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>360</v>
+        <v>383</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I111">
         <f>F111*VALUE(LEFT(H111, FIND(":", H111)-1))</f>
@@ -6369,10 +6697,10 @@
         <v>1</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>361</v>
+        <v>384</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I112">
         <f>F112*VALUE(LEFT(H112, FIND(":", H112)-1))</f>
@@ -6401,7 +6729,7 @@
         <v>1</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>429</v>
+        <v>452</v>
       </c>
       <c r="I113">
         <f>F113*VALUE(LEFT(H113, FIND(":", H113)-1))</f>
@@ -6424,16 +6752,16 @@
         <v>288</v>
       </c>
       <c r="E114" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F114">
         <v>1</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>362</v>
+        <v>385</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>422</v>
+        <v>445</v>
       </c>
       <c r="I114">
         <f>F114*VALUE(LEFT(H114, FIND(":", H114)-1))</f>
@@ -6456,13 +6784,13 @@
         <v>289</v>
       </c>
       <c r="E115" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F115">
         <v>1</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>430</v>
+        <v>453</v>
       </c>
       <c r="I115">
         <f>F115*VALUE(LEFT(H115, FIND(":", H115)-1))</f>
@@ -6485,16 +6813,16 @@
         <v>290</v>
       </c>
       <c r="E116" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F116">
         <v>1</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I116">
         <f>F116*VALUE(LEFT(H116, FIND(":", H116)-1))</f>
@@ -6525,10 +6853,10 @@
         <v>1</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I117">
         <f>F117*VALUE(LEFT(H117, FIND(":", H117)-1))</f>
@@ -6557,10 +6885,10 @@
         <v>1</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>365</v>
+        <v>388</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I118">
         <f>F118*VALUE(LEFT(H118, FIND(":", H118)-1))</f>
@@ -6589,10 +6917,10 @@
         <v>1</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>366</v>
+        <v>389</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I119">
         <f>F119*VALUE(LEFT(H119, FIND(":", H119)-1))</f>
@@ -6621,10 +6949,10 @@
         <v>1</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>367</v>
+        <v>390</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I120">
         <f>F120*VALUE(LEFT(H120, FIND(":", H120)-1))</f>
@@ -6647,16 +6975,16 @@
         <v>295</v>
       </c>
       <c r="E121" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F121">
         <v>1</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>368</v>
+        <v>391</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I121">
         <f>F121*VALUE(LEFT(H121, FIND(":", H121)-1))</f>
@@ -6679,13 +7007,13 @@
         <v>296</v>
       </c>
       <c r="E122" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F122">
         <v>1</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>422</v>
+        <v>445</v>
       </c>
       <c r="I122">
         <f>F122*VALUE(LEFT(H122, FIND(":", H122)-1))</f>
@@ -6714,10 +7042,10 @@
         <v>1</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>369</v>
+        <v>392</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I123">
         <f>F123*VALUE(LEFT(H123, FIND(":", H123)-1))</f>
@@ -6742,16 +7070,16 @@
         <v>298</v>
       </c>
       <c r="E124" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F124">
         <v>1</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>370</v>
+        <v>393</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I124">
         <f>F124*VALUE(LEFT(H124, FIND(":", H124)-1))</f>
@@ -6780,10 +7108,10 @@
         <v>1</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>371</v>
+        <v>394</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I125">
         <f>F125*VALUE(LEFT(H125, FIND(":", H125)-1))</f>
@@ -6812,10 +7140,10 @@
         <v>1</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>372</v>
+        <v>395</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I126">
         <f>F126*VALUE(LEFT(H126, FIND(":", H126)-1))</f>
@@ -6844,10 +7172,10 @@
         <v>1</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>373</v>
+        <v>396</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I127">
         <f>F127*VALUE(LEFT(H127, FIND(":", H127)-1))</f>
@@ -6876,10 +7204,10 @@
         <v>1</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>374</v>
+        <v>397</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I128">
         <f>F128*VALUE(LEFT(H128, FIND(":", H128)-1))</f>
@@ -6902,13 +7230,13 @@
         <v>303</v>
       </c>
       <c r="E129" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F129">
         <v>1</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>429</v>
+        <v>452</v>
       </c>
       <c r="I129">
         <f>F129*VALUE(LEFT(H129, FIND(":", H129)-1))</f>
@@ -6935,16 +7263,16 @@
         <v>304</v>
       </c>
       <c r="E130" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F130">
         <v>1</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>375</v>
+        <v>398</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I130">
         <f>F130*VALUE(LEFT(H130, FIND(":", H130)-1))</f>
@@ -6967,16 +7295,16 @@
         <v>305</v>
       </c>
       <c r="E131" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F131">
         <v>1</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>376</v>
+        <v>399</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>423</v>
+        <v>442</v>
       </c>
       <c r="I131">
         <f>F131*VALUE(LEFT(H131, FIND(":", H131)-1))</f>
@@ -6999,16 +7327,16 @@
         <v>306</v>
       </c>
       <c r="E132" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F132">
         <v>1</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>377</v>
+        <v>400</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I132">
         <f>F132*VALUE(LEFT(H132, FIND(":", H132)-1))</f>
@@ -7031,13 +7359,13 @@
         <v>307</v>
       </c>
       <c r="E133" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F133">
         <v>1</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>431</v>
+        <v>454</v>
       </c>
       <c r="I133">
         <f>F133*VALUE(LEFT(H133, FIND(":", H133)-1))</f>
@@ -7060,16 +7388,16 @@
         <v>308</v>
       </c>
       <c r="E134" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F134">
         <v>1</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>378</v>
+        <v>401</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="I134">
         <f>F134*VALUE(LEFT(H134, FIND(":", H134)-1))</f>
@@ -7110,7 +7438,7 @@
     <mergeCell ref="B124:B129"/>
     <mergeCell ref="B130:B134"/>
   </mergeCells>
-  <dataValidations count="133">
+  <dataValidations count="132">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2">
       <formula1>"0: 0 items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
@@ -7127,37 +7455,37 @@
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H8">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H9">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H10">
-      <formula1>"0: No items completed,5: 1 item completed,10: 2 items completed"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H11">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H12">
-      <formula1>"0: Not done,10: Defined"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H13">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H14">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H16">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H17">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H18">
       <formula1>"0: Low Maturity (0-9),4: Developing (10-18),7: Established (19-26),10: Optimizing (27-31)"</formula1>
@@ -7193,22 +7521,19 @@
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H29">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H30">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H31">
-      <formula1>"0: Not done,10: Done and clearly defined"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H32">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H33">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H34">
-      <formula1>"0: Not done,10: Defined"</formula1>
+      <formula1>"0: Low Maturity. Score Range (0-14),4: Developing. Score Range (15-30),7: Established. Score Range (31-42),10: Optimizing. Score Range (43-50)"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H35">
       <formula1>"0: No executive sponsor identified,10: Executive sponsor formally identified and actively engaged"</formula1>
@@ -7223,7 +7548,7 @@
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H39">
-      <formula1>"0: Does not exist,10: Exists"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H40">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
@@ -7262,19 +7587,19 @@
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H52">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H53">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H54">
-      <formula1>"0: Not done,10: Policy in place and published"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H55">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H56">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H57">
       <formula1>"0: Not done,10: Policy in place and published"</formula1>
